--- a/selenium-tests/reports/excel/report.xlsx
+++ b/selenium-tests/reports/excel/report.xlsx
@@ -20,7 +20,7 @@
     <t>Report Generation Date:</t>
   </si>
   <si>
-    <t>11/6/2026, 1:42:47 pm</t>
+    <t>13/6/2026, 12:22:36 pm</t>
   </si>
   <si>
     <t>Target Environment:</t>
@@ -80,7 +80,7 @@
     <t>Total Run Duration</t>
   </si>
   <si>
-    <t>194.24 seconds</t>
+    <t>311.03 seconds</t>
   </si>
   <si>
     <t/>
@@ -1430,7 +1430,7 @@
         <v>35</v>
       </c>
       <c r="F2" s="12">
-        <v>3386</v>
+        <v>3964</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>36</v>
@@ -1456,7 +1456,7 @@
         <v>35</v>
       </c>
       <c r="F3" s="12">
-        <v>1699</v>
+        <v>1942</v>
       </c>
       <c r="G3" s="13" t="s">
         <v>36</v>
@@ -1482,7 +1482,7 @@
         <v>35</v>
       </c>
       <c r="F4" s="12">
-        <v>388</v>
+        <v>683</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>36</v>
@@ -1508,7 +1508,7 @@
         <v>35</v>
       </c>
       <c r="F5" s="12">
-        <v>3203</v>
+        <v>4919</v>
       </c>
       <c r="G5" s="13" t="s">
         <v>36</v>
@@ -1534,7 +1534,7 @@
         <v>35</v>
       </c>
       <c r="F6" s="12">
-        <v>1406</v>
+        <v>2448</v>
       </c>
       <c r="G6" s="13" t="s">
         <v>36</v>
@@ -1560,7 +1560,7 @@
         <v>35</v>
       </c>
       <c r="F7" s="12">
-        <v>2352</v>
+        <v>4412</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>36</v>
@@ -1586,7 +1586,7 @@
         <v>35</v>
       </c>
       <c r="F8" s="12">
-        <v>2274</v>
+        <v>2625</v>
       </c>
       <c r="G8" s="13" t="s">
         <v>36</v>
@@ -1612,7 +1612,7 @@
         <v>35</v>
       </c>
       <c r="F9" s="12">
-        <v>1780</v>
+        <v>10184</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>36</v>
@@ -1638,7 +1638,7 @@
         <v>35</v>
       </c>
       <c r="F10" s="12">
-        <v>4647</v>
+        <v>10209</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>36</v>
@@ -1664,7 +1664,7 @@
         <v>35</v>
       </c>
       <c r="F11" s="12">
-        <v>788</v>
+        <v>10214</v>
       </c>
       <c r="G11" s="13" t="s">
         <v>36</v>
@@ -1690,7 +1690,7 @@
         <v>35</v>
       </c>
       <c r="F12" s="12">
-        <v>113</v>
+        <v>235</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>36</v>
@@ -1716,7 +1716,7 @@
         <v>35</v>
       </c>
       <c r="F13" s="12">
-        <v>331</v>
+        <v>356</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>36</v>
@@ -1742,7 +1742,7 @@
         <v>35</v>
       </c>
       <c r="F14" s="12">
-        <v>349</v>
+        <v>399</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>36</v>
@@ -1768,7 +1768,7 @@
         <v>35</v>
       </c>
       <c r="F15" s="12">
-        <v>325</v>
+        <v>427</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>36</v>
@@ -1794,7 +1794,7 @@
         <v>35</v>
       </c>
       <c r="F16" s="12">
-        <v>201</v>
+        <v>372</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>36</v>
@@ -1820,7 +1820,7 @@
         <v>35</v>
       </c>
       <c r="F17" s="12">
-        <v>207</v>
+        <v>559</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>36</v>
@@ -1846,7 +1846,7 @@
         <v>35</v>
       </c>
       <c r="F18" s="12">
-        <v>391</v>
+        <v>408</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>36</v>
@@ -1872,7 +1872,7 @@
         <v>35</v>
       </c>
       <c r="F19" s="12">
-        <v>138</v>
+        <v>279</v>
       </c>
       <c r="G19" s="13" t="s">
         <v>36</v>
@@ -1898,7 +1898,7 @@
         <v>35</v>
       </c>
       <c r="F20" s="12">
-        <v>2238</v>
+        <v>1724</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>36</v>
@@ -1924,7 +1924,7 @@
         <v>35</v>
       </c>
       <c r="F21" s="12">
-        <v>263</v>
+        <v>1020</v>
       </c>
       <c r="G21" s="13" t="s">
         <v>36</v>
@@ -1950,7 +1950,7 @@
         <v>35</v>
       </c>
       <c r="F22" s="12">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>36</v>
@@ -1976,7 +1976,7 @@
         <v>35</v>
       </c>
       <c r="F23" s="12">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>36</v>
@@ -2002,7 +2002,7 @@
         <v>35</v>
       </c>
       <c r="F24" s="12">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>36</v>
@@ -2028,7 +2028,7 @@
         <v>35</v>
       </c>
       <c r="F25" s="12">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>36</v>
@@ -2080,7 +2080,7 @@
         <v>35</v>
       </c>
       <c r="F27" s="12">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>36</v>
@@ -2106,7 +2106,7 @@
         <v>35</v>
       </c>
       <c r="F28" s="12">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>36</v>
@@ -2132,7 +2132,7 @@
         <v>35</v>
       </c>
       <c r="F29" s="12">
-        <v>3916</v>
+        <v>4396</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>36</v>
@@ -2158,7 +2158,7 @@
         <v>35</v>
       </c>
       <c r="F30" s="12">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>36</v>
@@ -2184,7 +2184,7 @@
         <v>35</v>
       </c>
       <c r="F31" s="12">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>36</v>
@@ -2210,7 +2210,7 @@
         <v>35</v>
       </c>
       <c r="F32" s="12">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="G32" s="13" t="s">
         <v>36</v>
@@ -2236,7 +2236,7 @@
         <v>35</v>
       </c>
       <c r="F33" s="12">
-        <v>1200</v>
+        <v>1253</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>36</v>
@@ -2262,7 +2262,7 @@
         <v>35</v>
       </c>
       <c r="F34" s="12">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="G34" s="13" t="s">
         <v>36</v>
@@ -2288,7 +2288,7 @@
         <v>35</v>
       </c>
       <c r="F35" s="12">
-        <v>664</v>
+        <v>687</v>
       </c>
       <c r="G35" s="13" t="s">
         <v>36</v>
@@ -2314,7 +2314,7 @@
         <v>35</v>
       </c>
       <c r="F36" s="12">
-        <v>1168</v>
+        <v>1207</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>36</v>
@@ -2340,7 +2340,7 @@
         <v>35</v>
       </c>
       <c r="F37" s="12">
-        <v>3128</v>
+        <v>3505</v>
       </c>
       <c r="G37" s="13" t="s">
         <v>36</v>
@@ -2366,7 +2366,7 @@
         <v>35</v>
       </c>
       <c r="F38" s="12">
-        <v>3505</v>
+        <v>3498</v>
       </c>
       <c r="G38" s="13" t="s">
         <v>36</v>
@@ -2392,7 +2392,7 @@
         <v>35</v>
       </c>
       <c r="F39" s="12">
-        <v>1157</v>
+        <v>1211</v>
       </c>
       <c r="G39" s="13" t="s">
         <v>36</v>
@@ -2418,7 +2418,7 @@
         <v>35</v>
       </c>
       <c r="F40" s="12">
-        <v>3094</v>
+        <v>3445</v>
       </c>
       <c r="G40" s="13" t="s">
         <v>36</v>
@@ -2444,7 +2444,7 @@
         <v>35</v>
       </c>
       <c r="F41" s="12">
-        <v>5116</v>
+        <v>4893</v>
       </c>
       <c r="G41" s="13" t="s">
         <v>36</v>
@@ -2470,7 +2470,7 @@
         <v>35</v>
       </c>
       <c r="F42" s="12">
-        <v>3580</v>
+        <v>3533</v>
       </c>
       <c r="G42" s="13" t="s">
         <v>36</v>
@@ -2496,7 +2496,7 @@
         <v>35</v>
       </c>
       <c r="F43" s="12">
-        <v>1315</v>
+        <v>1278</v>
       </c>
       <c r="G43" s="13" t="s">
         <v>36</v>
@@ -2522,7 +2522,7 @@
         <v>35</v>
       </c>
       <c r="F44" s="12">
-        <v>4678</v>
+        <v>4523</v>
       </c>
       <c r="G44" s="13" t="s">
         <v>36</v>
@@ -2548,7 +2548,7 @@
         <v>35</v>
       </c>
       <c r="F45" s="12">
-        <v>17651</v>
+        <v>17812</v>
       </c>
       <c r="G45" s="13" t="s">
         <v>36</v>
@@ -2574,7 +2574,7 @@
         <v>35</v>
       </c>
       <c r="F46" s="12">
-        <v>2568</v>
+        <v>2439</v>
       </c>
       <c r="G46" s="13" t="s">
         <v>36</v>
@@ -2600,7 +2600,7 @@
         <v>35</v>
       </c>
       <c r="F47" s="12">
-        <v>5797</v>
+        <v>6107</v>
       </c>
       <c r="G47" s="13" t="s">
         <v>36</v>
@@ -2626,7 +2626,7 @@
         <v>35</v>
       </c>
       <c r="F48" s="12">
-        <v>8105</v>
+        <v>8161</v>
       </c>
       <c r="G48" s="13" t="s">
         <v>36</v>
@@ -2652,7 +2652,7 @@
         <v>35</v>
       </c>
       <c r="F49" s="12">
-        <v>5056</v>
+        <v>5007</v>
       </c>
       <c r="G49" s="13" t="s">
         <v>36</v>
@@ -2678,7 +2678,7 @@
         <v>35</v>
       </c>
       <c r="F50" s="12">
-        <v>5126</v>
+        <v>5163</v>
       </c>
       <c r="G50" s="13" t="s">
         <v>36</v>
@@ -2704,7 +2704,7 @@
         <v>35</v>
       </c>
       <c r="F51" s="12">
-        <v>9836</v>
+        <v>10019</v>
       </c>
       <c r="G51" s="13" t="s">
         <v>36</v>
@@ -2730,7 +2730,7 @@
         <v>35</v>
       </c>
       <c r="F52" s="12">
-        <v>387</v>
+        <v>952</v>
       </c>
       <c r="G52" s="13" t="s">
         <v>36</v>
@@ -2756,7 +2756,7 @@
         <v>35</v>
       </c>
       <c r="F53" s="12">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="G53" s="13" t="s">
         <v>36</v>
@@ -2782,7 +2782,7 @@
         <v>35</v>
       </c>
       <c r="F54" s="12">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G54" s="13" t="s">
         <v>36</v>
@@ -2808,7 +2808,7 @@
         <v>35</v>
       </c>
       <c r="F55" s="12">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="G55" s="13" t="s">
         <v>36</v>
@@ -2834,7 +2834,7 @@
         <v>35</v>
       </c>
       <c r="F56" s="12">
-        <v>1302</v>
+        <v>2047</v>
       </c>
       <c r="G56" s="13" t="s">
         <v>36</v>
@@ -2860,7 +2860,7 @@
         <v>35</v>
       </c>
       <c r="F57" s="12">
-        <v>1130</v>
+        <v>1228</v>
       </c>
       <c r="G57" s="13" t="s">
         <v>36</v>
@@ -2886,7 +2886,7 @@
         <v>35</v>
       </c>
       <c r="F58" s="12">
-        <v>1114</v>
+        <v>1191</v>
       </c>
       <c r="G58" s="13" t="s">
         <v>36</v>
@@ -2912,7 +2912,7 @@
         <v>35</v>
       </c>
       <c r="F59" s="12">
-        <v>1190</v>
+        <v>1199</v>
       </c>
       <c r="G59" s="13" t="s">
         <v>36</v>
@@ -2938,7 +2938,7 @@
         <v>35</v>
       </c>
       <c r="F60" s="12">
-        <v>385</v>
+        <v>750</v>
       </c>
       <c r="G60" s="13" t="s">
         <v>36</v>
@@ -2964,7 +2964,7 @@
         <v>35</v>
       </c>
       <c r="F61" s="12">
-        <v>1714</v>
+        <v>2190</v>
       </c>
       <c r="G61" s="13" t="s">
         <v>36</v>
@@ -2990,7 +2990,7 @@
         <v>35</v>
       </c>
       <c r="F62" s="12">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="G62" s="13" t="s">
         <v>36</v>
@@ -3016,7 +3016,7 @@
         <v>35</v>
       </c>
       <c r="F63" s="12">
-        <v>1119</v>
+        <v>1596</v>
       </c>
       <c r="G63" s="13" t="s">
         <v>36</v>
@@ -3042,7 +3042,7 @@
         <v>35</v>
       </c>
       <c r="F64" s="12">
-        <v>139</v>
+        <v>596</v>
       </c>
       <c r="G64" s="13" t="s">
         <v>36</v>
@@ -3068,7 +3068,7 @@
         <v>35</v>
       </c>
       <c r="F65" s="12">
-        <v>549</v>
+        <v>466</v>
       </c>
       <c r="G65" s="13" t="s">
         <v>36</v>
@@ -3094,7 +3094,7 @@
         <v>35</v>
       </c>
       <c r="F66" s="12">
-        <v>82</v>
+        <v>520</v>
       </c>
       <c r="G66" s="13" t="s">
         <v>36</v>
@@ -3120,7 +3120,7 @@
         <v>35</v>
       </c>
       <c r="F67" s="12">
-        <v>290</v>
+        <v>96</v>
       </c>
       <c r="G67" s="13" t="s">
         <v>36</v>
@@ -3146,7 +3146,7 @@
         <v>35</v>
       </c>
       <c r="F68" s="12">
-        <v>1138</v>
+        <v>1214</v>
       </c>
       <c r="G68" s="13" t="s">
         <v>36</v>
@@ -3172,7 +3172,7 @@
         <v>35</v>
       </c>
       <c r="F69" s="12">
-        <v>1304</v>
+        <v>1740</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>36</v>
@@ -3198,7 +3198,7 @@
         <v>35</v>
       </c>
       <c r="F70" s="12">
-        <v>2055</v>
+        <v>2096</v>
       </c>
       <c r="G70" s="13" t="s">
         <v>36</v>
@@ -3224,7 +3224,7 @@
         <v>35</v>
       </c>
       <c r="F71" s="12">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G71" s="13" t="s">
         <v>36</v>
@@ -3250,7 +3250,7 @@
         <v>35</v>
       </c>
       <c r="F72" s="12">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="G72" s="13" t="s">
         <v>36</v>
@@ -3276,7 +3276,7 @@
         <v>35</v>
       </c>
       <c r="F73" s="12">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="G73" s="13" t="s">
         <v>36</v>
@@ -3302,7 +3302,7 @@
         <v>35</v>
       </c>
       <c r="F74" s="12">
-        <v>357</v>
+        <v>282</v>
       </c>
       <c r="G74" s="13" t="s">
         <v>36</v>
@@ -3328,7 +3328,7 @@
         <v>35</v>
       </c>
       <c r="F75" s="12">
-        <v>904</v>
+        <v>797</v>
       </c>
       <c r="G75" s="13" t="s">
         <v>36</v>
@@ -3354,7 +3354,7 @@
         <v>35</v>
       </c>
       <c r="F76" s="12">
-        <v>928</v>
+        <v>855</v>
       </c>
       <c r="G76" s="13" t="s">
         <v>36</v>
@@ -3406,7 +3406,7 @@
         <v>35</v>
       </c>
       <c r="F78" s="12">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="G78" s="13" t="s">
         <v>36</v>
@@ -3432,7 +3432,7 @@
         <v>35</v>
       </c>
       <c r="F79" s="12">
-        <v>946</v>
+        <v>805</v>
       </c>
       <c r="G79" s="13" t="s">
         <v>36</v>
@@ -3458,7 +3458,7 @@
         <v>35</v>
       </c>
       <c r="F80" s="12">
-        <v>472</v>
+        <v>151</v>
       </c>
       <c r="G80" s="13" t="s">
         <v>36</v>
@@ -3484,7 +3484,7 @@
         <v>35</v>
       </c>
       <c r="F81" s="12">
-        <v>191</v>
+        <v>10155</v>
       </c>
       <c r="G81" s="13" t="s">
         <v>36</v>
@@ -3510,7 +3510,7 @@
         <v>35</v>
       </c>
       <c r="F82" s="12">
-        <v>2116</v>
+        <v>10706</v>
       </c>
       <c r="G82" s="13" t="s">
         <v>36</v>
@@ -3536,7 +3536,7 @@
         <v>35</v>
       </c>
       <c r="F83" s="12">
-        <v>475</v>
+        <v>10165</v>
       </c>
       <c r="G83" s="13" t="s">
         <v>36</v>
@@ -3562,7 +3562,7 @@
         <v>35</v>
       </c>
       <c r="F84" s="12">
-        <v>7225</v>
+        <v>10574</v>
       </c>
       <c r="G84" s="13" t="s">
         <v>36</v>
@@ -3588,7 +3588,7 @@
         <v>35</v>
       </c>
       <c r="F85" s="12">
-        <v>1508</v>
+        <v>16845</v>
       </c>
       <c r="G85" s="13" t="s">
         <v>36</v>
@@ -3614,7 +3614,7 @@
         <v>35</v>
       </c>
       <c r="F86" s="12">
-        <v>8768</v>
+        <v>10565</v>
       </c>
       <c r="G86" s="13" t="s">
         <v>36</v>
@@ -3640,7 +3640,7 @@
         <v>35</v>
       </c>
       <c r="F87" s="12">
-        <v>2117</v>
+        <v>10040</v>
       </c>
       <c r="G87" s="13" t="s">
         <v>36</v>
@@ -3666,7 +3666,7 @@
         <v>35</v>
       </c>
       <c r="F88" s="12">
-        <v>5125</v>
+        <v>16060</v>
       </c>
       <c r="G88" s="13" t="s">
         <v>36</v>
@@ -3692,7 +3692,7 @@
         <v>35</v>
       </c>
       <c r="F89" s="12">
-        <v>292</v>
+        <v>392</v>
       </c>
       <c r="G89" s="13" t="s">
         <v>36</v>
@@ -3718,7 +3718,7 @@
         <v>35</v>
       </c>
       <c r="F90" s="12">
-        <v>2615</v>
+        <v>2732</v>
       </c>
       <c r="G90" s="13" t="s">
         <v>36</v>
@@ -3744,7 +3744,7 @@
         <v>35</v>
       </c>
       <c r="F91" s="12">
-        <v>2551</v>
+        <v>2785</v>
       </c>
       <c r="G91" s="13" t="s">
         <v>36</v>
@@ -3770,7 +3770,7 @@
         <v>35</v>
       </c>
       <c r="F92" s="12">
-        <v>1506</v>
+        <v>1519</v>
       </c>
       <c r="G92" s="13" t="s">
         <v>36</v>
@@ -3796,7 +3796,7 @@
         <v>35</v>
       </c>
       <c r="F93" s="12">
-        <v>1323</v>
+        <v>1626</v>
       </c>
       <c r="G93" s="13" t="s">
         <v>36</v>
@@ -3822,7 +3822,7 @@
         <v>35</v>
       </c>
       <c r="F94" s="12">
-        <v>843</v>
+        <v>1229</v>
       </c>
       <c r="G94" s="13" t="s">
         <v>36</v>
@@ -3848,7 +3848,7 @@
         <v>35</v>
       </c>
       <c r="F95" s="12">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="G95" s="13" t="s">
         <v>36</v>
@@ -3874,7 +3874,7 @@
         <v>35</v>
       </c>
       <c r="F96" s="12">
-        <v>793</v>
+        <v>906</v>
       </c>
       <c r="G96" s="13" t="s">
         <v>36</v>
@@ -3900,7 +3900,7 @@
         <v>35</v>
       </c>
       <c r="F97" s="12">
-        <v>1237</v>
+        <v>2195</v>
       </c>
       <c r="G97" s="13" t="s">
         <v>36</v>
@@ -3926,7 +3926,7 @@
         <v>35</v>
       </c>
       <c r="F98" s="12">
-        <v>3793</v>
+        <v>6047</v>
       </c>
       <c r="G98" s="13" t="s">
         <v>36</v>
@@ -3952,7 +3952,7 @@
         <v>35</v>
       </c>
       <c r="F99" s="12">
-        <v>6547</v>
+        <v>8282</v>
       </c>
       <c r="G99" s="13" t="s">
         <v>36</v>
@@ -3978,7 +3978,7 @@
         <v>35</v>
       </c>
       <c r="F100" s="12">
-        <v>2977</v>
+        <v>3287</v>
       </c>
       <c r="G100" s="13" t="s">
         <v>36</v>
@@ -4004,7 +4004,7 @@
         <v>35</v>
       </c>
       <c r="F101" s="12">
-        <v>4263</v>
+        <v>8646</v>
       </c>
       <c r="G101" s="13" t="s">
         <v>36</v>
@@ -4030,7 +4030,7 @@
         <v>35</v>
       </c>
       <c r="F102" s="12">
-        <v>410</v>
+        <v>2064</v>
       </c>
       <c r="G102" s="13" t="s">
         <v>36</v>
@@ -4056,7 +4056,7 @@
         <v>35</v>
       </c>
       <c r="F103" s="12">
-        <v>157</v>
+        <v>254</v>
       </c>
       <c r="G103" s="13" t="s">
         <v>36</v>
@@ -4082,7 +4082,7 @@
         <v>35</v>
       </c>
       <c r="F104" s="12">
-        <v>483</v>
+        <v>1042</v>
       </c>
       <c r="G104" s="13" t="s">
         <v>36</v>
@@ -4108,7 +4108,7 @@
         <v>35</v>
       </c>
       <c r="F105" s="12">
-        <v>3427</v>
+        <v>3775</v>
       </c>
       <c r="G105" s="13" t="s">
         <v>36</v>

--- a/selenium-tests/reports/excel/report.xlsx
+++ b/selenium-tests/reports/excel/report.xlsx
@@ -20,7 +20,7 @@
     <t>Report Generation Date:</t>
   </si>
   <si>
-    <t>13/6/2026, 12:22:36 pm</t>
+    <t>14/6/2026, 12:58:02 pm</t>
   </si>
   <si>
     <t>Target Environment:</t>
@@ -80,7 +80,7 @@
     <t>Total Run Duration</t>
   </si>
   <si>
-    <t>311.03 seconds</t>
+    <t>273.60 seconds</t>
   </si>
   <si>
     <t/>
@@ -1430,7 +1430,7 @@
         <v>35</v>
       </c>
       <c r="F2" s="12">
-        <v>3964</v>
+        <v>3627</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>36</v>
@@ -1456,7 +1456,7 @@
         <v>35</v>
       </c>
       <c r="F3" s="12">
-        <v>1942</v>
+        <v>1969</v>
       </c>
       <c r="G3" s="13" t="s">
         <v>36</v>
@@ -1482,7 +1482,7 @@
         <v>35</v>
       </c>
       <c r="F4" s="12">
-        <v>683</v>
+        <v>390</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>36</v>
@@ -1508,7 +1508,7 @@
         <v>35</v>
       </c>
       <c r="F5" s="12">
-        <v>4919</v>
+        <v>2940</v>
       </c>
       <c r="G5" s="13" t="s">
         <v>36</v>
@@ -1534,7 +1534,7 @@
         <v>35</v>
       </c>
       <c r="F6" s="12">
-        <v>2448</v>
+        <v>1468</v>
       </c>
       <c r="G6" s="13" t="s">
         <v>36</v>
@@ -1560,7 +1560,7 @@
         <v>35</v>
       </c>
       <c r="F7" s="12">
-        <v>4412</v>
+        <v>2010</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>36</v>
@@ -1586,7 +1586,7 @@
         <v>35</v>
       </c>
       <c r="F8" s="12">
-        <v>2625</v>
+        <v>2194</v>
       </c>
       <c r="G8" s="13" t="s">
         <v>36</v>
@@ -1612,7 +1612,7 @@
         <v>35</v>
       </c>
       <c r="F9" s="12">
-        <v>10184</v>
+        <v>1582</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>36</v>
@@ -1638,7 +1638,7 @@
         <v>35</v>
       </c>
       <c r="F10" s="12">
-        <v>10209</v>
+        <v>3765</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>36</v>
@@ -1664,7 +1664,7 @@
         <v>35</v>
       </c>
       <c r="F11" s="12">
-        <v>10214</v>
+        <v>759</v>
       </c>
       <c r="G11" s="13" t="s">
         <v>36</v>
@@ -1690,7 +1690,7 @@
         <v>35</v>
       </c>
       <c r="F12" s="12">
-        <v>235</v>
+        <v>97</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>36</v>
@@ -1716,7 +1716,7 @@
         <v>35</v>
       </c>
       <c r="F13" s="12">
-        <v>356</v>
+        <v>101</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>36</v>
@@ -1742,7 +1742,7 @@
         <v>35</v>
       </c>
       <c r="F14" s="12">
-        <v>399</v>
+        <v>244</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>36</v>
@@ -1768,7 +1768,7 @@
         <v>35</v>
       </c>
       <c r="F15" s="12">
-        <v>427</v>
+        <v>190</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>36</v>
@@ -1794,7 +1794,7 @@
         <v>35</v>
       </c>
       <c r="F16" s="12">
-        <v>372</v>
+        <v>178</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>36</v>
@@ -1820,7 +1820,7 @@
         <v>35</v>
       </c>
       <c r="F17" s="12">
-        <v>559</v>
+        <v>170</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>36</v>
@@ -1846,7 +1846,7 @@
         <v>35</v>
       </c>
       <c r="F18" s="12">
-        <v>408</v>
+        <v>185</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>36</v>
@@ -1872,7 +1872,7 @@
         <v>35</v>
       </c>
       <c r="F19" s="12">
-        <v>279</v>
+        <v>151</v>
       </c>
       <c r="G19" s="13" t="s">
         <v>36</v>
@@ -1898,7 +1898,7 @@
         <v>35</v>
       </c>
       <c r="F20" s="12">
-        <v>1724</v>
+        <v>983</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>36</v>
@@ -1924,7 +1924,7 @@
         <v>35</v>
       </c>
       <c r="F21" s="12">
-        <v>1020</v>
+        <v>207</v>
       </c>
       <c r="G21" s="13" t="s">
         <v>36</v>
@@ -1950,7 +1950,7 @@
         <v>35</v>
       </c>
       <c r="F22" s="12">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>36</v>
@@ -1976,7 +1976,7 @@
         <v>35</v>
       </c>
       <c r="F23" s="12">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>36</v>
@@ -2002,7 +2002,7 @@
         <v>35</v>
       </c>
       <c r="F24" s="12">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>36</v>
@@ -2028,7 +2028,7 @@
         <v>35</v>
       </c>
       <c r="F25" s="12">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>36</v>
@@ -2054,7 +2054,7 @@
         <v>35</v>
       </c>
       <c r="F26" s="12">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>36</v>
@@ -2080,7 +2080,7 @@
         <v>35</v>
       </c>
       <c r="F27" s="12">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>36</v>
@@ -2106,7 +2106,7 @@
         <v>35</v>
       </c>
       <c r="F28" s="12">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>36</v>
@@ -2132,7 +2132,7 @@
         <v>35</v>
       </c>
       <c r="F29" s="12">
-        <v>4396</v>
+        <v>3712</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>36</v>
@@ -2158,7 +2158,7 @@
         <v>35</v>
       </c>
       <c r="F30" s="12">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>36</v>
@@ -2184,7 +2184,7 @@
         <v>35</v>
       </c>
       <c r="F31" s="12">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>36</v>
@@ -2210,7 +2210,7 @@
         <v>35</v>
       </c>
       <c r="F32" s="12">
-        <v>174</v>
+        <v>241</v>
       </c>
       <c r="G32" s="13" t="s">
         <v>36</v>
@@ -2236,7 +2236,7 @@
         <v>35</v>
       </c>
       <c r="F33" s="12">
-        <v>1253</v>
+        <v>1126</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>36</v>
@@ -2262,7 +2262,7 @@
         <v>35</v>
       </c>
       <c r="F34" s="12">
-        <v>138</v>
+        <v>69</v>
       </c>
       <c r="G34" s="13" t="s">
         <v>36</v>
@@ -2288,7 +2288,7 @@
         <v>35</v>
       </c>
       <c r="F35" s="12">
-        <v>687</v>
+        <v>653</v>
       </c>
       <c r="G35" s="13" t="s">
         <v>36</v>
@@ -2314,7 +2314,7 @@
         <v>35</v>
       </c>
       <c r="F36" s="12">
-        <v>1207</v>
+        <v>1149</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>36</v>
@@ -2340,7 +2340,7 @@
         <v>35</v>
       </c>
       <c r="F37" s="12">
-        <v>3505</v>
+        <v>2682</v>
       </c>
       <c r="G37" s="13" t="s">
         <v>36</v>
@@ -2366,7 +2366,7 @@
         <v>35</v>
       </c>
       <c r="F38" s="12">
-        <v>3498</v>
+        <v>3246</v>
       </c>
       <c r="G38" s="13" t="s">
         <v>36</v>
@@ -2392,7 +2392,7 @@
         <v>35</v>
       </c>
       <c r="F39" s="12">
-        <v>1211</v>
+        <v>1109</v>
       </c>
       <c r="G39" s="13" t="s">
         <v>36</v>
@@ -2418,7 +2418,7 @@
         <v>35</v>
       </c>
       <c r="F40" s="12">
-        <v>3445</v>
+        <v>2600</v>
       </c>
       <c r="G40" s="13" t="s">
         <v>36</v>
@@ -2444,7 +2444,7 @@
         <v>35</v>
       </c>
       <c r="F41" s="12">
-        <v>4893</v>
+        <v>4438</v>
       </c>
       <c r="G41" s="13" t="s">
         <v>36</v>
@@ -2470,7 +2470,7 @@
         <v>35</v>
       </c>
       <c r="F42" s="12">
-        <v>3533</v>
+        <v>3194</v>
       </c>
       <c r="G42" s="13" t="s">
         <v>36</v>
@@ -2496,7 +2496,7 @@
         <v>35</v>
       </c>
       <c r="F43" s="12">
-        <v>1278</v>
+        <v>1013</v>
       </c>
       <c r="G43" s="13" t="s">
         <v>36</v>
@@ -2522,7 +2522,7 @@
         <v>35</v>
       </c>
       <c r="F44" s="12">
-        <v>4523</v>
+        <v>4040</v>
       </c>
       <c r="G44" s="13" t="s">
         <v>36</v>
@@ -2548,7 +2548,7 @@
         <v>35</v>
       </c>
       <c r="F45" s="12">
-        <v>17812</v>
+        <v>17383</v>
       </c>
       <c r="G45" s="13" t="s">
         <v>36</v>
@@ -2574,7 +2574,7 @@
         <v>35</v>
       </c>
       <c r="F46" s="12">
-        <v>2439</v>
+        <v>2270</v>
       </c>
       <c r="G46" s="13" t="s">
         <v>36</v>
@@ -2600,7 +2600,7 @@
         <v>35</v>
       </c>
       <c r="F47" s="12">
-        <v>6107</v>
+        <v>5416</v>
       </c>
       <c r="G47" s="13" t="s">
         <v>36</v>
@@ -2626,7 +2626,7 @@
         <v>35</v>
       </c>
       <c r="F48" s="12">
-        <v>8161</v>
+        <v>8064</v>
       </c>
       <c r="G48" s="13" t="s">
         <v>36</v>
@@ -2652,7 +2652,7 @@
         <v>35</v>
       </c>
       <c r="F49" s="12">
-        <v>5007</v>
+        <v>4318</v>
       </c>
       <c r="G49" s="13" t="s">
         <v>36</v>
@@ -2678,7 +2678,7 @@
         <v>35</v>
       </c>
       <c r="F50" s="12">
-        <v>5163</v>
+        <v>5122</v>
       </c>
       <c r="G50" s="13" t="s">
         <v>36</v>
@@ -2704,7 +2704,7 @@
         <v>35</v>
       </c>
       <c r="F51" s="12">
-        <v>10019</v>
+        <v>9581</v>
       </c>
       <c r="G51" s="13" t="s">
         <v>36</v>
@@ -2730,7 +2730,7 @@
         <v>35</v>
       </c>
       <c r="F52" s="12">
-        <v>952</v>
+        <v>360</v>
       </c>
       <c r="G52" s="13" t="s">
         <v>36</v>
@@ -2756,7 +2756,7 @@
         <v>35</v>
       </c>
       <c r="F53" s="12">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="G53" s="13" t="s">
         <v>36</v>
@@ -2782,7 +2782,7 @@
         <v>35</v>
       </c>
       <c r="F54" s="12">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="G54" s="13" t="s">
         <v>36</v>
@@ -2808,7 +2808,7 @@
         <v>35</v>
       </c>
       <c r="F55" s="12">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="G55" s="13" t="s">
         <v>36</v>
@@ -2834,7 +2834,7 @@
         <v>35</v>
       </c>
       <c r="F56" s="12">
-        <v>2047</v>
+        <v>1494</v>
       </c>
       <c r="G56" s="13" t="s">
         <v>36</v>
@@ -2860,7 +2860,7 @@
         <v>35</v>
       </c>
       <c r="F57" s="12">
-        <v>1228</v>
+        <v>1117</v>
       </c>
       <c r="G57" s="13" t="s">
         <v>36</v>
@@ -2886,7 +2886,7 @@
         <v>35</v>
       </c>
       <c r="F58" s="12">
-        <v>1191</v>
+        <v>1185</v>
       </c>
       <c r="G58" s="13" t="s">
         <v>36</v>
@@ -2912,7 +2912,7 @@
         <v>35</v>
       </c>
       <c r="F59" s="12">
-        <v>1199</v>
+        <v>1120</v>
       </c>
       <c r="G59" s="13" t="s">
         <v>36</v>
@@ -2938,7 +2938,7 @@
         <v>35</v>
       </c>
       <c r="F60" s="12">
-        <v>750</v>
+        <v>490</v>
       </c>
       <c r="G60" s="13" t="s">
         <v>36</v>
@@ -2964,7 +2964,7 @@
         <v>35</v>
       </c>
       <c r="F61" s="12">
-        <v>2190</v>
+        <v>1575</v>
       </c>
       <c r="G61" s="13" t="s">
         <v>36</v>
@@ -2990,7 +2990,7 @@
         <v>35</v>
       </c>
       <c r="F62" s="12">
-        <v>1594</v>
+        <v>1591</v>
       </c>
       <c r="G62" s="13" t="s">
         <v>36</v>
@@ -3016,7 +3016,7 @@
         <v>35</v>
       </c>
       <c r="F63" s="12">
-        <v>1596</v>
+        <v>878</v>
       </c>
       <c r="G63" s="13" t="s">
         <v>36</v>
@@ -3042,7 +3042,7 @@
         <v>35</v>
       </c>
       <c r="F64" s="12">
-        <v>596</v>
+        <v>493</v>
       </c>
       <c r="G64" s="13" t="s">
         <v>36</v>
@@ -3068,7 +3068,7 @@
         <v>35</v>
       </c>
       <c r="F65" s="12">
-        <v>466</v>
+        <v>337</v>
       </c>
       <c r="G65" s="13" t="s">
         <v>36</v>
@@ -3094,7 +3094,7 @@
         <v>35</v>
       </c>
       <c r="F66" s="12">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="G66" s="13" t="s">
         <v>36</v>
@@ -3120,7 +3120,7 @@
         <v>35</v>
       </c>
       <c r="F67" s="12">
-        <v>96</v>
+        <v>254</v>
       </c>
       <c r="G67" s="13" t="s">
         <v>36</v>
@@ -3146,7 +3146,7 @@
         <v>35</v>
       </c>
       <c r="F68" s="12">
-        <v>1214</v>
+        <v>1114</v>
       </c>
       <c r="G68" s="13" t="s">
         <v>36</v>
@@ -3172,7 +3172,7 @@
         <v>35</v>
       </c>
       <c r="F69" s="12">
-        <v>1740</v>
+        <v>10814</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>36</v>
@@ -3198,7 +3198,7 @@
         <v>35</v>
       </c>
       <c r="F70" s="12">
-        <v>2096</v>
+        <v>17212</v>
       </c>
       <c r="G70" s="13" t="s">
         <v>36</v>
@@ -3224,7 +3224,7 @@
         <v>35</v>
       </c>
       <c r="F71" s="12">
-        <v>59</v>
+        <v>10036</v>
       </c>
       <c r="G71" s="13" t="s">
         <v>36</v>
@@ -3250,7 +3250,7 @@
         <v>35</v>
       </c>
       <c r="F72" s="12">
-        <v>84</v>
+        <v>10027</v>
       </c>
       <c r="G72" s="13" t="s">
         <v>36</v>
@@ -3276,7 +3276,7 @@
         <v>35</v>
       </c>
       <c r="F73" s="12">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="G73" s="13" t="s">
         <v>36</v>
@@ -3302,7 +3302,7 @@
         <v>35</v>
       </c>
       <c r="F74" s="12">
-        <v>282</v>
+        <v>10137</v>
       </c>
       <c r="G74" s="13" t="s">
         <v>36</v>
@@ -3328,7 +3328,7 @@
         <v>35</v>
       </c>
       <c r="F75" s="12">
-        <v>797</v>
+        <v>10034</v>
       </c>
       <c r="G75" s="13" t="s">
         <v>36</v>
@@ -3354,7 +3354,7 @@
         <v>35</v>
       </c>
       <c r="F76" s="12">
-        <v>855</v>
+        <v>10011</v>
       </c>
       <c r="G76" s="13" t="s">
         <v>36</v>
@@ -3380,7 +3380,7 @@
         <v>35</v>
       </c>
       <c r="F77" s="12">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="G77" s="13" t="s">
         <v>36</v>
@@ -3406,7 +3406,7 @@
         <v>35</v>
       </c>
       <c r="F78" s="12">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="G78" s="13" t="s">
         <v>36</v>
@@ -3432,7 +3432,7 @@
         <v>35</v>
       </c>
       <c r="F79" s="12">
-        <v>805</v>
+        <v>10028</v>
       </c>
       <c r="G79" s="13" t="s">
         <v>36</v>
@@ -3458,7 +3458,7 @@
         <v>35</v>
       </c>
       <c r="F80" s="12">
-        <v>151</v>
+        <v>7</v>
       </c>
       <c r="G80" s="13" t="s">
         <v>36</v>
@@ -3484,7 +3484,7 @@
         <v>35</v>
       </c>
       <c r="F81" s="12">
-        <v>10155</v>
+        <v>151</v>
       </c>
       <c r="G81" s="13" t="s">
         <v>36</v>
@@ -3510,7 +3510,7 @@
         <v>35</v>
       </c>
       <c r="F82" s="12">
-        <v>10706</v>
+        <v>2182</v>
       </c>
       <c r="G82" s="13" t="s">
         <v>36</v>
@@ -3536,7 +3536,7 @@
         <v>35</v>
       </c>
       <c r="F83" s="12">
-        <v>10165</v>
+        <v>487</v>
       </c>
       <c r="G83" s="13" t="s">
         <v>36</v>
@@ -3562,7 +3562,7 @@
         <v>35</v>
       </c>
       <c r="F84" s="12">
-        <v>10574</v>
+        <v>6687</v>
       </c>
       <c r="G84" s="13" t="s">
         <v>36</v>
@@ -3588,7 +3588,7 @@
         <v>35</v>
       </c>
       <c r="F85" s="12">
-        <v>16845</v>
+        <v>1509</v>
       </c>
       <c r="G85" s="13" t="s">
         <v>36</v>
@@ -3614,7 +3614,7 @@
         <v>35</v>
       </c>
       <c r="F86" s="12">
-        <v>10565</v>
+        <v>8103</v>
       </c>
       <c r="G86" s="13" t="s">
         <v>36</v>
@@ -3640,7 +3640,7 @@
         <v>35</v>
       </c>
       <c r="F87" s="12">
-        <v>10040</v>
+        <v>2113</v>
       </c>
       <c r="G87" s="13" t="s">
         <v>36</v>
@@ -3666,7 +3666,7 @@
         <v>35</v>
       </c>
       <c r="F88" s="12">
-        <v>16060</v>
+        <v>5129</v>
       </c>
       <c r="G88" s="13" t="s">
         <v>36</v>
@@ -3692,7 +3692,7 @@
         <v>35</v>
       </c>
       <c r="F89" s="12">
-        <v>392</v>
+        <v>303</v>
       </c>
       <c r="G89" s="13" t="s">
         <v>36</v>
@@ -3718,7 +3718,7 @@
         <v>35</v>
       </c>
       <c r="F90" s="12">
-        <v>2732</v>
+        <v>2604</v>
       </c>
       <c r="G90" s="13" t="s">
         <v>36</v>
@@ -3744,7 +3744,7 @@
         <v>35</v>
       </c>
       <c r="F91" s="12">
-        <v>2785</v>
+        <v>2453</v>
       </c>
       <c r="G91" s="13" t="s">
         <v>36</v>
@@ -3770,7 +3770,7 @@
         <v>35</v>
       </c>
       <c r="F92" s="12">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="G92" s="13" t="s">
         <v>36</v>
@@ -3796,7 +3796,7 @@
         <v>35</v>
       </c>
       <c r="F93" s="12">
-        <v>1626</v>
+        <v>1302</v>
       </c>
       <c r="G93" s="13" t="s">
         <v>36</v>
@@ -3822,7 +3822,7 @@
         <v>35</v>
       </c>
       <c r="F94" s="12">
-        <v>1229</v>
+        <v>829</v>
       </c>
       <c r="G94" s="13" t="s">
         <v>36</v>
@@ -3848,7 +3848,7 @@
         <v>35</v>
       </c>
       <c r="F95" s="12">
-        <v>185</v>
+        <v>10054</v>
       </c>
       <c r="G95" s="13" t="s">
         <v>36</v>
@@ -3874,7 +3874,7 @@
         <v>35</v>
       </c>
       <c r="F96" s="12">
-        <v>906</v>
+        <v>54</v>
       </c>
       <c r="G96" s="13" t="s">
         <v>36</v>
@@ -3900,7 +3900,7 @@
         <v>35</v>
       </c>
       <c r="F97" s="12">
-        <v>2195</v>
+        <v>1462</v>
       </c>
       <c r="G97" s="13" t="s">
         <v>36</v>
@@ -3926,7 +3926,7 @@
         <v>35</v>
       </c>
       <c r="F98" s="12">
-        <v>6047</v>
+        <v>2908</v>
       </c>
       <c r="G98" s="13" t="s">
         <v>36</v>
@@ -3952,7 +3952,7 @@
         <v>35</v>
       </c>
       <c r="F99" s="12">
-        <v>8282</v>
+        <v>6279</v>
       </c>
       <c r="G99" s="13" t="s">
         <v>36</v>
@@ -3978,7 +3978,7 @@
         <v>35</v>
       </c>
       <c r="F100" s="12">
-        <v>3287</v>
+        <v>2717</v>
       </c>
       <c r="G100" s="13" t="s">
         <v>36</v>
@@ -4004,7 +4004,7 @@
         <v>35</v>
       </c>
       <c r="F101" s="12">
-        <v>8646</v>
+        <v>4518</v>
       </c>
       <c r="G101" s="13" t="s">
         <v>36</v>
@@ -4030,7 +4030,7 @@
         <v>35</v>
       </c>
       <c r="F102" s="12">
-        <v>2064</v>
+        <v>508</v>
       </c>
       <c r="G102" s="13" t="s">
         <v>36</v>
@@ -4056,7 +4056,7 @@
         <v>35</v>
       </c>
       <c r="F103" s="12">
-        <v>254</v>
+        <v>140</v>
       </c>
       <c r="G103" s="13" t="s">
         <v>36</v>
@@ -4082,7 +4082,7 @@
         <v>35</v>
       </c>
       <c r="F104" s="12">
-        <v>1042</v>
+        <v>442</v>
       </c>
       <c r="G104" s="13" t="s">
         <v>36</v>
@@ -4108,7 +4108,7 @@
         <v>35</v>
       </c>
       <c r="F105" s="12">
-        <v>3775</v>
+        <v>3307</v>
       </c>
       <c r="G105" s="13" t="s">
         <v>36</v>

--- a/selenium-tests/reports/excel/report.xlsx
+++ b/selenium-tests/reports/excel/report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="445">
   <si>
     <t>MedMonitor E2E Test Suite Summary</t>
   </si>
@@ -20,7 +20,7 @@
     <t>Report Generation Date:</t>
   </si>
   <si>
-    <t>14/6/2026, 12:58:02 pm</t>
+    <t>18/6/2026, 5:27:06 pm</t>
   </si>
   <si>
     <t>Target Environment:</t>
@@ -80,7 +80,7 @@
     <t>Total Run Duration</t>
   </si>
   <si>
-    <t>273.60 seconds</t>
+    <t>371.11 seconds</t>
   </si>
   <si>
     <t/>
@@ -179,6 +179,66 @@
     <t>Session persistence preserves caregiver mode on page refresh</t>
   </si>
   <si>
+    <t>Test 1.11</t>
+  </si>
+  <si>
+    <t>Verify password input fields use type="password"</t>
+  </si>
+  <si>
+    <t>Test 1.12</t>
+  </si>
+  <si>
+    <t>Verify registration form contains confirm password input labels</t>
+  </si>
+  <si>
+    <t>Test 1.13</t>
+  </si>
+  <si>
+    <t>Verify presence of custom brand login graphics/illustrations</t>
+  </si>
+  <si>
+    <t>Test 1.14</t>
+  </si>
+  <si>
+    <t>Verify sign-in page contains link to Register page</t>
+  </si>
+  <si>
+    <t>Test 1.15</t>
+  </si>
+  <si>
+    <t>Verify Register page contains link to Sign In page</t>
+  </si>
+  <si>
+    <t>Test 1.16</t>
+  </si>
+  <si>
+    <t>Verify error messages close properly when user clicks close button</t>
+  </si>
+  <si>
+    <t>Test 1.17</t>
+  </si>
+  <si>
+    <t>Verify register submit button styling matches main theme</t>
+  </si>
+  <si>
+    <t>Test 1.18</t>
+  </si>
+  <si>
+    <t>Verify local login input boxes have correct custom placeholders</t>
+  </si>
+  <si>
+    <t>Test 1.19</t>
+  </si>
+  <si>
+    <t>Verify mode selection titles correctly guide user roles</t>
+  </si>
+  <si>
+    <t>Test 1.20</t>
+  </si>
+  <si>
+    <t>Verify persistent sessions across double refresh on patient dashboard</t>
+  </si>
+  <si>
     <t>Test 2.1</t>
   </si>
   <si>
@@ -242,6 +302,66 @@
     <t>Navigation via Caregiver sidebar to Alerts feed</t>
   </si>
   <si>
+    <t>Test 2.11</t>
+  </si>
+  <si>
+    <t>Verify navigation sidebar has toggle button</t>
+  </si>
+  <si>
+    <t>Test 2.12</t>
+  </si>
+  <si>
+    <t>Verify active menu item displays proper active visual indicator</t>
+  </si>
+  <si>
+    <t>Test 2.13</t>
+  </si>
+  <si>
+    <t>Verify hovering over patient menu items triggers pointer indicators</t>
+  </si>
+  <si>
+    <t>Test 2.14</t>
+  </si>
+  <si>
+    <t>Verify profile screen header is visible</t>
+  </si>
+  <si>
+    <t>Test 2.15</t>
+  </si>
+  <si>
+    <t>Verify navigation to invalid path redirects user correctly</t>
+  </si>
+  <si>
+    <t>Test 2.16</t>
+  </si>
+  <si>
+    <t>Verify app logo redirects user back to dashboard</t>
+  </si>
+  <si>
+    <t>Test 2.17</t>
+  </si>
+  <si>
+    <t>Verify caregiver sidebar navigation options are distinct from patient options</t>
+  </si>
+  <si>
+    <t>Test 2.18</t>
+  </si>
+  <si>
+    <t>Verify caregiver settings page link is present in caregiver sidebar</t>
+  </si>
+  <si>
+    <t>Test 2.19</t>
+  </si>
+  <si>
+    <t>Verify browser history back action works correctly between screens</t>
+  </si>
+  <si>
+    <t>Test 2.20</t>
+  </si>
+  <si>
+    <t>Verify sidebar responsive drawer layouts under mobile viewports</t>
+  </si>
+  <si>
     <t>Test 3.1</t>
   </si>
   <si>
@@ -305,6 +425,66 @@
     <t>Caregiver Dashboard Live Activity feed visibility</t>
   </si>
   <si>
+    <t>Test 3.11</t>
+  </si>
+  <si>
+    <t>Verify greeting matches time of day (e.g., "Good Morning", "Good Afternoon")</t>
+  </si>
+  <si>
+    <t>Test 3.12</t>
+  </si>
+  <si>
+    <t>Verify greeting text displays logged-in patient name</t>
+  </si>
+  <si>
+    <t>Test 3.13</t>
+  </si>
+  <si>
+    <t>Verify dashboard streak badge displays correct numeric label</t>
+  </si>
+  <si>
+    <t>Test 3.14</t>
+  </si>
+  <si>
+    <t>Verify Quick Add Med card contains an action button</t>
+  </si>
+  <si>
+    <t>Test 3.15</t>
+  </si>
+  <si>
+    <t>Verify Quick Care Circle card renders active layout list</t>
+  </si>
+  <si>
+    <t>Test 3.16</t>
+  </si>
+  <si>
+    <t>Verify Quick Inventory card renders warnings for low items</t>
+  </si>
+  <si>
+    <t>Test 3.17</t>
+  </si>
+  <si>
+    <t>Verify Caregiver Dashboard header text visibility</t>
+  </si>
+  <si>
+    <t>Test 3.18</t>
+  </si>
+  <si>
+    <t>Verify Caregiver Dashboard lists managed patient records</t>
+  </si>
+  <si>
+    <t>Test 3.19</t>
+  </si>
+  <si>
+    <t>Verify layout grid counts on dashboard statistics metrics</t>
+  </si>
+  <si>
+    <t>Test 3.20</t>
+  </si>
+  <si>
+    <t>Verify dashboard quick links have tooltips</t>
+  </si>
+  <si>
     <t>Test 4.1</t>
   </si>
   <si>
@@ -428,6 +608,66 @@
     <t>Delete the second medicine card and check empty list</t>
   </si>
   <si>
+    <t>Test 4.21</t>
+  </si>
+  <si>
+    <t>Verify Add Medicine modal has close button on top-right</t>
+  </si>
+  <si>
+    <t>Test 4.22</t>
+  </si>
+  <si>
+    <t>Verify dosage inputs restrict negative numeric entries</t>
+  </si>
+  <si>
+    <t>Test 4.23</t>
+  </si>
+  <si>
+    <t>Verify dosage unit input has correct helper text placeholder (e.g., "mg")</t>
+  </si>
+  <si>
+    <t>Test 4.24</t>
+  </si>
+  <si>
+    <t>Verify slots checkboxes (Morning, Afternoon, Night) default to unchecked</t>
+  </si>
+  <si>
+    <t>Test 4.25</t>
+  </si>
+  <si>
+    <t>Verify start date input defaults to current system date</t>
+  </si>
+  <si>
+    <t>Test 4.26</t>
+  </si>
+  <si>
+    <t>Verify low stock warning limit inputs default to 5</t>
+  </si>
+  <si>
+    <t>Test 4.27</t>
+  </si>
+  <si>
+    <t>Verify search input dynamically filters out mismatched medicine cards</t>
+  </si>
+  <si>
+    <t>Test 4.28</t>
+  </si>
+  <si>
+    <t>Verify editing a medicine card preserves other unmodified details</t>
+  </si>
+  <si>
+    <t>Test 4.29</t>
+  </si>
+  <si>
+    <t>Verify search box placeholder text matches cabinet specifications</t>
+  </si>
+  <si>
+    <t>Test 4.30</t>
+  </si>
+  <si>
+    <t>Verify layout container uses custom responsive grid layout</t>
+  </si>
+  <si>
     <t>Test 5.1</t>
   </si>
   <si>
@@ -479,6 +719,48 @@
     <t>Caregiver Alerts filter Due Now clicks successfully</t>
   </si>
   <si>
+    <t>Test 5.9</t>
+  </si>
+  <si>
+    <t>Verify missed doses sections display warnings</t>
+  </si>
+  <si>
+    <t>Test 5.10</t>
+  </si>
+  <si>
+    <t>Verify due now alerts display check/take actions</t>
+  </si>
+  <si>
+    <t>Test 5.11</t>
+  </si>
+  <si>
+    <t>Verify upcoming alerts section shows dates clearly</t>
+  </si>
+  <si>
+    <t>Test 5.12</t>
+  </si>
+  <si>
+    <t>Verify alert container displays alert severity colors (red/green/yellow)</t>
+  </si>
+  <si>
+    <t>Test 5.13</t>
+  </si>
+  <si>
+    <t>Verify caregiver alerts search bar filters alerts dynamically</t>
+  </si>
+  <si>
+    <t>Test 5.14</t>
+  </si>
+  <si>
+    <t>Verify caregiver alerts filter count matches active conditions</t>
+  </si>
+  <si>
+    <t>Test 5.15</t>
+  </si>
+  <si>
+    <t>Verify alert detail popovers show full medication names</t>
+  </si>
+  <si>
     <t>Test 6.1</t>
   </si>
   <si>
@@ -512,6 +794,66 @@
     <t>Caregiver Analytics compliance statistics widget visibility</t>
   </si>
   <si>
+    <t>Test 6.6</t>
+  </si>
+  <si>
+    <t>Verify weekly adherence chart canvas renders correctly</t>
+  </si>
+  <si>
+    <t>Test 6.7</t>
+  </si>
+  <si>
+    <t>Verify adherence trend chart has interactive legend details</t>
+  </si>
+  <si>
+    <t>Test 6.8</t>
+  </si>
+  <si>
+    <t>Verify compliance status pie chart legend matches current meds</t>
+  </si>
+  <si>
+    <t>Test 6.9</t>
+  </si>
+  <si>
+    <t>Verify caregiver compliance summary report title text</t>
+  </si>
+  <si>
+    <t>Test 6.10</t>
+  </si>
+  <si>
+    <t>Verify empty analytics screen displays proper descriptive illustrations</t>
+  </si>
+  <si>
+    <t>Test 6.11</t>
+  </si>
+  <si>
+    <t>Verify chart controls allow switching between weeks</t>
+  </si>
+  <si>
+    <t>Test 6.12</t>
+  </si>
+  <si>
+    <t>Verify analytics summary statistics contain % metrics</t>
+  </si>
+  <si>
+    <t>Test 6.13</t>
+  </si>
+  <si>
+    <t>Verify page container fits properly inside main screen</t>
+  </si>
+  <si>
+    <t>Test 6.14</t>
+  </si>
+  <si>
+    <t>Verify caregiver analytics has select patient filters</t>
+  </si>
+  <si>
+    <t>Test 6.15</t>
+  </si>
+  <si>
+    <t>Verify analytics page shows loading skeletons when queries execute</t>
+  </si>
+  <si>
     <t>Test 7.1</t>
   </si>
   <si>
@@ -563,6 +905,48 @@
     <t>Caregiver Reports verify layout displays reports container</t>
   </si>
   <si>
+    <t>Test 7.9</t>
+  </si>
+  <si>
+    <t>Verify PDF export action contains download details</t>
+  </si>
+  <si>
+    <t>Test 7.10</t>
+  </si>
+  <si>
+    <t>Verify report adherence summaries display compliance percentages</t>
+  </si>
+  <si>
+    <t>Test 7.11</t>
+  </si>
+  <si>
+    <t>Verify range filter dropdown lists all report frequencies</t>
+  </si>
+  <si>
+    <t>Test 7.12</t>
+  </si>
+  <si>
+    <t>Verify caregiver reports mockup matches reports grid layouts</t>
+  </si>
+  <si>
+    <t>Test 7.13</t>
+  </si>
+  <si>
+    <t>Verify caregiver reports screen displays "Export All Data" button</t>
+  </si>
+  <si>
+    <t>Test 7.14</t>
+  </si>
+  <si>
+    <t>Verify report tables have column headers (Date, Medicine, Status)</t>
+  </si>
+  <si>
+    <t>Test 7.15</t>
+  </si>
+  <si>
+    <t>Verify row clicks do not break report details</t>
+  </si>
+  <si>
     <t>Test 8.1</t>
   </si>
   <si>
@@ -614,6 +998,48 @@
     <t>Clear search input restores all stock items to view</t>
   </si>
   <si>
+    <t>Test 8.9</t>
+  </si>
+  <si>
+    <t>Verify search input field renders magnifying glass icon</t>
+  </si>
+  <si>
+    <t>Test 8.10</t>
+  </si>
+  <si>
+    <t>Verify low-stock items display alert badges</t>
+  </si>
+  <si>
+    <t>Test 8.11</t>
+  </si>
+  <si>
+    <t>Verify medicine entries list remaining tablet counts</t>
+  </si>
+  <si>
+    <t>Test 8.12</t>
+  </si>
+  <si>
+    <t>Verify clicking an inventory card opens quick-update view</t>
+  </si>
+  <si>
+    <t>Test 8.13</t>
+  </si>
+  <si>
+    <t>Verify empty state layouts show helper texts</t>
+  </si>
+  <si>
+    <t>Test 8.14</t>
+  </si>
+  <si>
+    <t>Verify refill requests button handles action responses</t>
+  </si>
+  <si>
+    <t>Test 8.15</t>
+  </si>
+  <si>
+    <t>Verify items table uses grid formatting</t>
+  </si>
+  <si>
     <t>Test 9.1</t>
   </si>
   <si>
@@ -665,6 +1091,48 @@
     <t>Verify deleted member card is removed from circle</t>
   </si>
   <si>
+    <t>Test 9.9</t>
+  </si>
+  <si>
+    <t>Verify Add Family Member modal inputs exist (Name, Relation, Contact)</t>
+  </si>
+  <si>
+    <t>Test 9.10</t>
+  </si>
+  <si>
+    <t>Verify relation dropdown includes spouse/parent/child categories</t>
+  </si>
+  <si>
+    <t>Test 9.11</t>
+  </si>
+  <si>
+    <t>Verify family member cards render communication buttons</t>
+  </si>
+  <si>
+    <t>Test 9.12</t>
+  </si>
+  <si>
+    <t>Verify primary caregiver tags highlight on cards</t>
+  </si>
+  <si>
+    <t>Test 9.13</t>
+  </si>
+  <si>
+    <t>Verify family member delete actions trigger confirm dialogue</t>
+  </si>
+  <si>
+    <t>Test 9.14</t>
+  </si>
+  <si>
+    <t>Verify modal window dismisses when clicking the background overlay</t>
+  </si>
+  <si>
+    <t>Test 9.15</t>
+  </si>
+  <si>
+    <t>Verify Care Circle layout matches card list grid specifications</t>
+  </si>
+  <si>
     <t>Test 10.1</t>
   </si>
   <si>
@@ -716,6 +1184,48 @@
     <t>Caregiver Dashboard container visibility check</t>
   </si>
   <si>
+    <t>Test 10.9</t>
+  </si>
+  <si>
+    <t>Verify patient listing displays patient phone and email info</t>
+  </si>
+  <si>
+    <t>Test 10.10</t>
+  </si>
+  <si>
+    <t>Verify dashboard activity logs render category icons</t>
+  </si>
+  <si>
+    <t>Test 10.11</t>
+  </si>
+  <si>
+    <t>Verify caregiver portal settings displays notifications toggles</t>
+  </si>
+  <si>
+    <t>Test 10.12</t>
+  </si>
+  <si>
+    <t>Verify caregiver profile details data changes save</t>
+  </si>
+  <si>
+    <t>Test 10.13</t>
+  </si>
+  <si>
+    <t>Verify active patient cards show adherence highlights</t>
+  </si>
+  <si>
+    <t>Test 10.14</t>
+  </si>
+  <si>
+    <t>Verify caregiver button appears on mode selection page</t>
+  </si>
+  <si>
+    <t>Test 10.15</t>
+  </si>
+  <si>
+    <t>Verify caregiver sidebar contains Patient Registry routing</t>
+  </si>
+  <si>
     <t>Test 11.1</t>
   </si>
   <si>
@@ -771,6 +1281,72 @@
   </si>
   <si>
     <t>Application base URL is reachable and redirects correctly</t>
+  </si>
+  <si>
+    <t>Test 11.10</t>
+  </si>
+  <si>
+    <t>Verify register passwords check safety strengths</t>
+  </si>
+  <si>
+    <t>Test 11.11</t>
+  </si>
+  <si>
+    <t>Verify dosage inputs block negative entries</t>
+  </si>
+  <si>
+    <t>Test 11.12</t>
+  </si>
+  <si>
+    <t>Verify validation warnings display beneath malformed email entries</t>
+  </si>
+  <si>
+    <t>Test 11.13</t>
+  </si>
+  <si>
+    <t>Verify invalid validation fields apply error styles</t>
+  </si>
+  <si>
+    <t>Test 11.14</t>
+  </si>
+  <si>
+    <t>Verify register handles already-registered addresses</t>
+  </si>
+  <si>
+    <t>Test 11.15</t>
+  </si>
+  <si>
+    <t>Verify family member phone inputs reject letters</t>
+  </si>
+  <si>
+    <t>Test 11.16</t>
+  </si>
+  <si>
+    <t>Verify validation warnings clear on reopen</t>
+  </si>
+  <si>
+    <t>Test 11.17</t>
+  </si>
+  <si>
+    <t>Verify login validation errors display dynamically</t>
+  </si>
+  <si>
+    <t>Test 11.18</t>
+  </si>
+  <si>
+    <t>Verify password mismatch error banner can be closed</t>
+  </si>
+  <si>
+    <t>Test 11.19</t>
+  </si>
+  <si>
+    <t>Verify date entry rules block invalid end dates</t>
+  </si>
+  <si>
+    <t>Test 11.20</t>
+  </si>
+  <si>
+    <t>Verify cancel clicks clear cached validation warning layouts</t>
   </si>
 </sst>
 </file>
@@ -1303,7 +1879,7 @@
         <v>10</v>
       </c>
       <c r="B8" s="6">
-        <v>104</v>
+        <v>200</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>11</v>
@@ -1314,7 +1890,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="6">
-        <v>104</v>
+        <v>200</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>13</v>
@@ -1375,7 +1951,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1430,7 +2006,7 @@
         <v>35</v>
       </c>
       <c r="F2" s="12">
-        <v>3627</v>
+        <v>3160</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>36</v>
@@ -1456,7 +2032,7 @@
         <v>35</v>
       </c>
       <c r="F3" s="12">
-        <v>1969</v>
+        <v>2174</v>
       </c>
       <c r="G3" s="13" t="s">
         <v>36</v>
@@ -1482,7 +2058,7 @@
         <v>35</v>
       </c>
       <c r="F4" s="12">
-        <v>390</v>
+        <v>494</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>36</v>
@@ -1508,7 +2084,7 @@
         <v>35</v>
       </c>
       <c r="F5" s="12">
-        <v>2940</v>
+        <v>3532</v>
       </c>
       <c r="G5" s="13" t="s">
         <v>36</v>
@@ -1534,7 +2110,7 @@
         <v>35</v>
       </c>
       <c r="F6" s="12">
-        <v>1468</v>
+        <v>1359</v>
       </c>
       <c r="G6" s="13" t="s">
         <v>36</v>
@@ -1560,7 +2136,7 @@
         <v>35</v>
       </c>
       <c r="F7" s="12">
-        <v>2010</v>
+        <v>2537</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>36</v>
@@ -1586,7 +2162,7 @@
         <v>35</v>
       </c>
       <c r="F8" s="12">
-        <v>2194</v>
+        <v>3083</v>
       </c>
       <c r="G8" s="13" t="s">
         <v>36</v>
@@ -1612,7 +2188,7 @@
         <v>35</v>
       </c>
       <c r="F9" s="12">
-        <v>1582</v>
+        <v>1701</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>36</v>
@@ -1638,7 +2214,7 @@
         <v>35</v>
       </c>
       <c r="F10" s="12">
-        <v>3765</v>
+        <v>3748</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>36</v>
@@ -1664,7 +2240,7 @@
         <v>35</v>
       </c>
       <c r="F11" s="12">
-        <v>759</v>
+        <v>1007</v>
       </c>
       <c r="G11" s="13" t="s">
         <v>36</v>
@@ -1678,11 +2254,11 @@
         <v>55</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="D12" s="11" t="s">
         <v>35</v>
       </c>
@@ -1690,7 +2266,7 @@
         <v>35</v>
       </c>
       <c r="F12" s="12">
-        <v>97</v>
+        <v>10141</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>36</v>
@@ -1701,14 +2277,14 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="D13" s="11" t="s">
         <v>35</v>
       </c>
@@ -1716,7 +2292,7 @@
         <v>35</v>
       </c>
       <c r="F13" s="12">
-        <v>101</v>
+        <v>10421</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>36</v>
@@ -1727,14 +2303,14 @@
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>61</v>
-      </c>
       <c r="D14" s="11" t="s">
         <v>35</v>
       </c>
@@ -1742,7 +2318,7 @@
         <v>35</v>
       </c>
       <c r="F14" s="12">
-        <v>244</v>
+        <v>109</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>36</v>
@@ -1753,14 +2329,14 @@
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>63</v>
-      </c>
       <c r="D15" s="11" t="s">
         <v>35</v>
       </c>
@@ -1768,7 +2344,7 @@
         <v>35</v>
       </c>
       <c r="F15" s="12">
-        <v>190</v>
+        <v>10327</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>36</v>
@@ -1779,14 +2355,14 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>65</v>
-      </c>
       <c r="D16" s="11" t="s">
         <v>35</v>
       </c>
@@ -1794,7 +2370,7 @@
         <v>35</v>
       </c>
       <c r="F16" s="12">
-        <v>178</v>
+        <v>10158</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>36</v>
@@ -1805,14 +2381,14 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>67</v>
-      </c>
       <c r="D17" s="11" t="s">
         <v>35</v>
       </c>
@@ -1820,7 +2396,7 @@
         <v>35</v>
       </c>
       <c r="F17" s="12">
-        <v>170</v>
+        <v>10334</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>36</v>
@@ -1831,14 +2407,14 @@
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="D18" s="11" t="s">
         <v>35</v>
       </c>
@@ -1846,7 +2422,7 @@
         <v>35</v>
       </c>
       <c r="F18" s="12">
-        <v>185</v>
+        <v>10315</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>36</v>
@@ -1857,14 +2433,14 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>71</v>
-      </c>
       <c r="D19" s="11" t="s">
         <v>35</v>
       </c>
@@ -1872,7 +2448,7 @@
         <v>35</v>
       </c>
       <c r="F19" s="12">
-        <v>151</v>
+        <v>10374</v>
       </c>
       <c r="G19" s="13" t="s">
         <v>36</v>
@@ -1883,14 +2459,14 @@
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>73</v>
-      </c>
       <c r="D20" s="11" t="s">
         <v>35</v>
       </c>
@@ -1898,7 +2474,7 @@
         <v>35</v>
       </c>
       <c r="F20" s="12">
-        <v>983</v>
+        <v>220</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>36</v>
@@ -1909,14 +2485,14 @@
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>75</v>
-      </c>
       <c r="D21" s="11" t="s">
         <v>35</v>
       </c>
@@ -1924,7 +2500,7 @@
         <v>35</v>
       </c>
       <c r="F21" s="12">
-        <v>207</v>
+        <v>10226</v>
       </c>
       <c r="G21" s="13" t="s">
         <v>36</v>
@@ -1935,14 +2511,14 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>78</v>
-      </c>
       <c r="D22" s="11" t="s">
         <v>35</v>
       </c>
@@ -1950,7 +2526,7 @@
         <v>35</v>
       </c>
       <c r="F22" s="12">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>36</v>
@@ -1961,14 +2537,14 @@
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>80</v>
-      </c>
       <c r="D23" s="11" t="s">
         <v>35</v>
       </c>
@@ -1976,7 +2552,7 @@
         <v>35</v>
       </c>
       <c r="F23" s="12">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>36</v>
@@ -1987,14 +2563,14 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="D24" s="11" t="s">
         <v>35</v>
       </c>
@@ -2002,7 +2578,7 @@
         <v>35</v>
       </c>
       <c r="F24" s="12">
-        <v>34</v>
+        <v>300</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>36</v>
@@ -2013,14 +2589,14 @@
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="D25" s="11" t="s">
         <v>35</v>
       </c>
@@ -2028,7 +2604,7 @@
         <v>35</v>
       </c>
       <c r="F25" s="12">
-        <v>17</v>
+        <v>245</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>36</v>
@@ -2039,14 +2615,14 @@
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>86</v>
-      </c>
       <c r="D26" s="11" t="s">
         <v>35</v>
       </c>
@@ -2054,7 +2630,7 @@
         <v>35</v>
       </c>
       <c r="F26" s="12">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>36</v>
@@ -2065,14 +2641,14 @@
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="D27" s="11" t="s">
         <v>35</v>
       </c>
@@ -2080,7 +2656,7 @@
         <v>35</v>
       </c>
       <c r="F27" s="12">
-        <v>30</v>
+        <v>189</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>36</v>
@@ -2091,14 +2667,14 @@
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="D28" s="11" t="s">
         <v>35</v>
       </c>
@@ -2106,7 +2682,7 @@
         <v>35</v>
       </c>
       <c r="F28" s="12">
-        <v>18</v>
+        <v>264</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>36</v>
@@ -2117,14 +2693,14 @@
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>92</v>
-      </c>
       <c r="D29" s="11" t="s">
         <v>35</v>
       </c>
@@ -2132,7 +2708,7 @@
         <v>35</v>
       </c>
       <c r="F29" s="12">
-        <v>3712</v>
+        <v>196</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>36</v>
@@ -2143,14 +2719,14 @@
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>94</v>
-      </c>
       <c r="D30" s="11" t="s">
         <v>35</v>
       </c>
@@ -2158,7 +2734,7 @@
         <v>35</v>
       </c>
       <c r="F30" s="12">
-        <v>41</v>
+        <v>1211</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>36</v>
@@ -2169,14 +2745,14 @@
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>96</v>
-      </c>
       <c r="D31" s="11" t="s">
         <v>35</v>
       </c>
@@ -2184,7 +2760,7 @@
         <v>35</v>
       </c>
       <c r="F31" s="12">
-        <v>22</v>
+        <v>450</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>36</v>
@@ -2195,14 +2771,14 @@
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>99</v>
-      </c>
       <c r="D32" s="11" t="s">
         <v>35</v>
       </c>
@@ -2210,7 +2786,7 @@
         <v>35</v>
       </c>
       <c r="F32" s="12">
-        <v>241</v>
+        <v>113</v>
       </c>
       <c r="G32" s="13" t="s">
         <v>36</v>
@@ -2221,13 +2797,13 @@
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>35</v>
@@ -2236,7 +2812,7 @@
         <v>35</v>
       </c>
       <c r="F33" s="12">
-        <v>1126</v>
+        <v>132</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>36</v>
@@ -2247,13 +2823,13 @@
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>35</v>
@@ -2262,7 +2838,7 @@
         <v>35</v>
       </c>
       <c r="F34" s="12">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="G34" s="13" t="s">
         <v>36</v>
@@ -2273,13 +2849,13 @@
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>35</v>
@@ -2288,7 +2864,7 @@
         <v>35</v>
       </c>
       <c r="F35" s="12">
-        <v>653</v>
+        <v>606</v>
       </c>
       <c r="G35" s="13" t="s">
         <v>36</v>
@@ -2299,13 +2875,13 @@
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>35</v>
@@ -2314,7 +2890,7 @@
         <v>35</v>
       </c>
       <c r="F36" s="12">
-        <v>1149</v>
+        <v>1072</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>36</v>
@@ -2325,13 +2901,13 @@
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>35</v>
@@ -2340,7 +2916,7 @@
         <v>35</v>
       </c>
       <c r="F37" s="12">
-        <v>2682</v>
+        <v>102</v>
       </c>
       <c r="G37" s="13" t="s">
         <v>36</v>
@@ -2351,13 +2927,13 @@
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>35</v>
@@ -2366,7 +2942,7 @@
         <v>35</v>
       </c>
       <c r="F38" s="12">
-        <v>3246</v>
+        <v>102</v>
       </c>
       <c r="G38" s="13" t="s">
         <v>36</v>
@@ -2377,13 +2953,13 @@
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>35</v>
@@ -2392,7 +2968,7 @@
         <v>35</v>
       </c>
       <c r="F39" s="12">
-        <v>1109</v>
+        <v>116</v>
       </c>
       <c r="G39" s="13" t="s">
         <v>36</v>
@@ -2403,13 +2979,13 @@
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D40" s="11" t="s">
         <v>35</v>
@@ -2418,7 +2994,7 @@
         <v>35</v>
       </c>
       <c r="F40" s="12">
-        <v>2600</v>
+        <v>723</v>
       </c>
       <c r="G40" s="13" t="s">
         <v>36</v>
@@ -2429,13 +3005,13 @@
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>35</v>
@@ -2444,7 +3020,7 @@
         <v>35</v>
       </c>
       <c r="F41" s="12">
-        <v>4438</v>
+        <v>914</v>
       </c>
       <c r="G41" s="13" t="s">
         <v>36</v>
@@ -2455,14 +3031,14 @@
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>119</v>
-      </c>
       <c r="D42" s="11" t="s">
         <v>35</v>
       </c>
@@ -2470,7 +3046,7 @@
         <v>35</v>
       </c>
       <c r="F42" s="12">
-        <v>3194</v>
+        <v>20</v>
       </c>
       <c r="G42" s="13" t="s">
         <v>36</v>
@@ -2481,14 +3057,14 @@
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="D43" s="11" t="s">
         <v>35</v>
       </c>
@@ -2496,7 +3072,7 @@
         <v>35</v>
       </c>
       <c r="F43" s="12">
-        <v>1013</v>
+        <v>20</v>
       </c>
       <c r="G43" s="13" t="s">
         <v>36</v>
@@ -2507,14 +3083,14 @@
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>123</v>
-      </c>
       <c r="D44" s="11" t="s">
         <v>35</v>
       </c>
@@ -2522,7 +3098,7 @@
         <v>35</v>
       </c>
       <c r="F44" s="12">
-        <v>4040</v>
+        <v>43</v>
       </c>
       <c r="G44" s="13" t="s">
         <v>36</v>
@@ -2533,14 +3109,14 @@
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>125</v>
-      </c>
       <c r="D45" s="11" t="s">
         <v>35</v>
       </c>
@@ -2548,7 +3124,7 @@
         <v>35</v>
       </c>
       <c r="F45" s="12">
-        <v>17383</v>
+        <v>21</v>
       </c>
       <c r="G45" s="13" t="s">
         <v>36</v>
@@ -2559,14 +3135,14 @@
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>127</v>
-      </c>
       <c r="D46" s="11" t="s">
         <v>35</v>
       </c>
@@ -2574,7 +3150,7 @@
         <v>35</v>
       </c>
       <c r="F46" s="12">
-        <v>2270</v>
+        <v>44</v>
       </c>
       <c r="G46" s="13" t="s">
         <v>36</v>
@@ -2585,14 +3161,14 @@
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>129</v>
-      </c>
       <c r="D47" s="11" t="s">
         <v>35</v>
       </c>
@@ -2600,7 +3176,7 @@
         <v>35</v>
       </c>
       <c r="F47" s="12">
-        <v>5416</v>
+        <v>20</v>
       </c>
       <c r="G47" s="13" t="s">
         <v>36</v>
@@ -2611,14 +3187,14 @@
     </row>
     <row r="48" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>131</v>
-      </c>
       <c r="D48" s="11" t="s">
         <v>35</v>
       </c>
@@ -2626,7 +3202,7 @@
         <v>35</v>
       </c>
       <c r="F48" s="12">
-        <v>8064</v>
+        <v>21</v>
       </c>
       <c r="G48" s="13" t="s">
         <v>36</v>
@@ -2637,14 +3213,14 @@
     </row>
     <row r="49" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>133</v>
-      </c>
       <c r="D49" s="11" t="s">
         <v>35</v>
       </c>
@@ -2652,7 +3228,7 @@
         <v>35</v>
       </c>
       <c r="F49" s="12">
-        <v>4318</v>
+        <v>4260</v>
       </c>
       <c r="G49" s="13" t="s">
         <v>36</v>
@@ -2663,14 +3239,14 @@
     </row>
     <row r="50" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>135</v>
-      </c>
       <c r="D50" s="11" t="s">
         <v>35</v>
       </c>
@@ -2678,7 +3254,7 @@
         <v>35</v>
       </c>
       <c r="F50" s="12">
-        <v>5122</v>
+        <v>27</v>
       </c>
       <c r="G50" s="13" t="s">
         <v>36</v>
@@ -2689,14 +3265,14 @@
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>137</v>
-      </c>
       <c r="D51" s="11" t="s">
         <v>35</v>
       </c>
@@ -2704,7 +3280,7 @@
         <v>35</v>
       </c>
       <c r="F51" s="12">
-        <v>9581</v>
+        <v>22</v>
       </c>
       <c r="G51" s="13" t="s">
         <v>36</v>
@@ -2715,14 +3291,14 @@
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>140</v>
-      </c>
       <c r="D52" s="11" t="s">
         <v>35</v>
       </c>
@@ -2730,7 +3306,7 @@
         <v>35</v>
       </c>
       <c r="F52" s="12">
-        <v>360</v>
+        <v>1163</v>
       </c>
       <c r="G52" s="13" t="s">
         <v>36</v>
@@ -2741,13 +3317,13 @@
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D53" s="11" t="s">
         <v>35</v>
@@ -2756,7 +3332,7 @@
         <v>35</v>
       </c>
       <c r="F53" s="12">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="G53" s="13" t="s">
         <v>36</v>
@@ -2767,13 +3343,13 @@
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D54" s="11" t="s">
         <v>35</v>
@@ -2782,7 +3358,7 @@
         <v>35</v>
       </c>
       <c r="F54" s="12">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="G54" s="13" t="s">
         <v>36</v>
@@ -2793,13 +3369,13 @@
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D55" s="11" t="s">
         <v>35</v>
@@ -2808,7 +3384,7 @@
         <v>35</v>
       </c>
       <c r="F55" s="12">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="G55" s="13" t="s">
         <v>36</v>
@@ -2819,13 +3395,13 @@
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D56" s="11" t="s">
         <v>35</v>
@@ -2834,7 +3410,7 @@
         <v>35</v>
       </c>
       <c r="F56" s="12">
-        <v>1494</v>
+        <v>23</v>
       </c>
       <c r="G56" s="13" t="s">
         <v>36</v>
@@ -2845,13 +3421,13 @@
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D57" s="11" t="s">
         <v>35</v>
@@ -2860,7 +3436,7 @@
         <v>35</v>
       </c>
       <c r="F57" s="12">
-        <v>1117</v>
+        <v>17</v>
       </c>
       <c r="G57" s="13" t="s">
         <v>36</v>
@@ -2871,13 +3447,13 @@
     </row>
     <row r="58" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>35</v>
@@ -2886,7 +3462,7 @@
         <v>35</v>
       </c>
       <c r="F58" s="12">
-        <v>1185</v>
+        <v>1145</v>
       </c>
       <c r="G58" s="13" t="s">
         <v>36</v>
@@ -2897,13 +3473,13 @@
     </row>
     <row r="59" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D59" s="11" t="s">
         <v>35</v>
@@ -2912,7 +3488,7 @@
         <v>35</v>
       </c>
       <c r="F59" s="12">
-        <v>1120</v>
+        <v>48</v>
       </c>
       <c r="G59" s="13" t="s">
         <v>36</v>
@@ -2923,13 +3499,13 @@
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D60" s="11" t="s">
         <v>35</v>
@@ -2938,7 +3514,7 @@
         <v>35</v>
       </c>
       <c r="F60" s="12">
-        <v>490</v>
+        <v>82</v>
       </c>
       <c r="G60" s="13" t="s">
         <v>36</v>
@@ -2949,14 +3525,14 @@
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B61" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C61" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="C61" s="5" t="s">
-        <v>159</v>
-      </c>
       <c r="D61" s="11" t="s">
         <v>35</v>
       </c>
@@ -2964,7 +3540,7 @@
         <v>35</v>
       </c>
       <c r="F61" s="12">
-        <v>1575</v>
+        <v>37</v>
       </c>
       <c r="G61" s="13" t="s">
         <v>36</v>
@@ -2975,13 +3551,13 @@
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D62" s="11" t="s">
         <v>35</v>
@@ -2990,7 +3566,7 @@
         <v>35</v>
       </c>
       <c r="F62" s="12">
-        <v>1591</v>
+        <v>134</v>
       </c>
       <c r="G62" s="13" t="s">
         <v>36</v>
@@ -3001,13 +3577,13 @@
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D63" s="11" t="s">
         <v>35</v>
@@ -3016,7 +3592,7 @@
         <v>35</v>
       </c>
       <c r="F63" s="12">
-        <v>878</v>
+        <v>1157</v>
       </c>
       <c r="G63" s="13" t="s">
         <v>36</v>
@@ -3027,13 +3603,13 @@
     </row>
     <row r="64" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D64" s="11" t="s">
         <v>35</v>
@@ -3042,7 +3618,7 @@
         <v>35</v>
       </c>
       <c r="F64" s="12">
-        <v>493</v>
+        <v>99</v>
       </c>
       <c r="G64" s="13" t="s">
         <v>36</v>
@@ -3053,13 +3629,13 @@
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D65" s="11" t="s">
         <v>35</v>
@@ -3068,7 +3644,7 @@
         <v>35</v>
       </c>
       <c r="F65" s="12">
-        <v>337</v>
+        <v>447</v>
       </c>
       <c r="G65" s="13" t="s">
         <v>36</v>
@@ -3079,14 +3655,14 @@
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B66" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>170</v>
-      </c>
       <c r="D66" s="11" t="s">
         <v>35</v>
       </c>
@@ -3094,7 +3670,7 @@
         <v>35</v>
       </c>
       <c r="F66" s="12">
-        <v>534</v>
+        <v>1120</v>
       </c>
       <c r="G66" s="13" t="s">
         <v>36</v>
@@ -3105,13 +3681,13 @@
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D67" s="11" t="s">
         <v>35</v>
@@ -3120,7 +3696,7 @@
         <v>35</v>
       </c>
       <c r="F67" s="12">
-        <v>254</v>
+        <v>2681</v>
       </c>
       <c r="G67" s="13" t="s">
         <v>36</v>
@@ -3131,13 +3707,13 @@
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D68" s="11" t="s">
         <v>35</v>
@@ -3146,7 +3722,7 @@
         <v>35</v>
       </c>
       <c r="F68" s="12">
-        <v>1114</v>
+        <v>3263</v>
       </c>
       <c r="G68" s="13" t="s">
         <v>36</v>
@@ -3157,13 +3733,13 @@
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D69" s="11" t="s">
         <v>35</v>
@@ -3172,7 +3748,7 @@
         <v>35</v>
       </c>
       <c r="F69" s="12">
-        <v>10814</v>
+        <v>1193</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>36</v>
@@ -3183,13 +3759,13 @@
     </row>
     <row r="70" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D70" s="11" t="s">
         <v>35</v>
@@ -3198,7 +3774,7 @@
         <v>35</v>
       </c>
       <c r="F70" s="12">
-        <v>17212</v>
+        <v>2901</v>
       </c>
       <c r="G70" s="13" t="s">
         <v>36</v>
@@ -3209,13 +3785,13 @@
     </row>
     <row r="71" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D71" s="11" t="s">
         <v>35</v>
@@ -3224,7 +3800,7 @@
         <v>35</v>
       </c>
       <c r="F71" s="12">
-        <v>10036</v>
+        <v>4587</v>
       </c>
       <c r="G71" s="13" t="s">
         <v>36</v>
@@ -3235,13 +3811,13 @@
     </row>
     <row r="72" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D72" s="11" t="s">
         <v>35</v>
@@ -3250,7 +3826,7 @@
         <v>35</v>
       </c>
       <c r="F72" s="12">
-        <v>10027</v>
+        <v>3257</v>
       </c>
       <c r="G72" s="13" t="s">
         <v>36</v>
@@ -3261,13 +3837,13 @@
     </row>
     <row r="73" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D73" s="11" t="s">
         <v>35</v>
@@ -3276,7 +3852,7 @@
         <v>35</v>
       </c>
       <c r="F73" s="12">
-        <v>14</v>
+        <v>1062</v>
       </c>
       <c r="G73" s="13" t="s">
         <v>36</v>
@@ -3287,13 +3863,13 @@
     </row>
     <row r="74" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D74" s="11" t="s">
         <v>35</v>
@@ -3302,7 +3878,7 @@
         <v>35</v>
       </c>
       <c r="F74" s="12">
-        <v>10137</v>
+        <v>4149</v>
       </c>
       <c r="G74" s="13" t="s">
         <v>36</v>
@@ -3313,13 +3889,13 @@
     </row>
     <row r="75" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D75" s="11" t="s">
         <v>35</v>
@@ -3328,7 +3904,7 @@
         <v>35</v>
       </c>
       <c r="F75" s="12">
-        <v>10034</v>
+        <v>17450</v>
       </c>
       <c r="G75" s="13" t="s">
         <v>36</v>
@@ -3339,13 +3915,13 @@
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D76" s="11" t="s">
         <v>35</v>
@@ -3354,7 +3930,7 @@
         <v>35</v>
       </c>
       <c r="F76" s="12">
-        <v>10011</v>
+        <v>2297</v>
       </c>
       <c r="G76" s="13" t="s">
         <v>36</v>
@@ -3365,13 +3941,13 @@
     </row>
     <row r="77" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D77" s="11" t="s">
         <v>35</v>
@@ -3380,7 +3956,7 @@
         <v>35</v>
       </c>
       <c r="F77" s="12">
-        <v>13</v>
+        <v>5554</v>
       </c>
       <c r="G77" s="13" t="s">
         <v>36</v>
@@ -3391,13 +3967,13 @@
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D78" s="11" t="s">
         <v>35</v>
@@ -3406,7 +3982,7 @@
         <v>35</v>
       </c>
       <c r="F78" s="12">
-        <v>13</v>
+        <v>8093</v>
       </c>
       <c r="G78" s="13" t="s">
         <v>36</v>
@@ -3417,13 +3993,13 @@
     </row>
     <row r="79" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D79" s="11" t="s">
         <v>35</v>
@@ -3432,7 +4008,7 @@
         <v>35</v>
       </c>
       <c r="F79" s="12">
-        <v>10028</v>
+        <v>4627</v>
       </c>
       <c r="G79" s="13" t="s">
         <v>36</v>
@@ -3443,13 +4019,13 @@
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D80" s="11" t="s">
         <v>35</v>
@@ -3458,7 +4034,7 @@
         <v>35</v>
       </c>
       <c r="F80" s="12">
-        <v>7</v>
+        <v>5109</v>
       </c>
       <c r="G80" s="13" t="s">
         <v>36</v>
@@ -3469,13 +4045,13 @@
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>201</v>
+        <v>158</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D81" s="11" t="s">
         <v>35</v>
@@ -3484,7 +4060,7 @@
         <v>35</v>
       </c>
       <c r="F81" s="12">
-        <v>151</v>
+        <v>9456</v>
       </c>
       <c r="G81" s="13" t="s">
         <v>36</v>
@@ -3495,13 +4071,13 @@
     </row>
     <row r="82" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>201</v>
+        <v>158</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D82" s="11" t="s">
         <v>35</v>
@@ -3510,7 +4086,7 @@
         <v>35</v>
       </c>
       <c r="F82" s="12">
-        <v>2182</v>
+        <v>1915</v>
       </c>
       <c r="G82" s="13" t="s">
         <v>36</v>
@@ -3521,14 +4097,14 @@
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B83" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C83" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="C83" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="D83" s="11" t="s">
         <v>35</v>
       </c>
@@ -3536,7 +4112,7 @@
         <v>35</v>
       </c>
       <c r="F83" s="12">
-        <v>487</v>
+        <v>1290</v>
       </c>
       <c r="G83" s="13" t="s">
         <v>36</v>
@@ -3547,13 +4123,13 @@
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>201</v>
+        <v>158</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D84" s="11" t="s">
         <v>35</v>
@@ -3562,7 +4138,7 @@
         <v>35</v>
       </c>
       <c r="F84" s="12">
-        <v>6687</v>
+        <v>1298</v>
       </c>
       <c r="G84" s="13" t="s">
         <v>36</v>
@@ -3573,13 +4149,13 @@
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>201</v>
+        <v>158</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D85" s="11" t="s">
         <v>35</v>
@@ -3588,7 +4164,7 @@
         <v>35</v>
       </c>
       <c r="F85" s="12">
-        <v>1509</v>
+        <v>1246</v>
       </c>
       <c r="G85" s="13" t="s">
         <v>36</v>
@@ -3599,13 +4175,13 @@
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>201</v>
+        <v>158</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D86" s="11" t="s">
         <v>35</v>
@@ -3614,7 +4190,7 @@
         <v>35</v>
       </c>
       <c r="F86" s="12">
-        <v>8103</v>
+        <v>1243</v>
       </c>
       <c r="G86" s="13" t="s">
         <v>36</v>
@@ -3625,13 +4201,13 @@
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>201</v>
+        <v>158</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D87" s="11" t="s">
         <v>35</v>
@@ -3640,7 +4216,7 @@
         <v>35</v>
       </c>
       <c r="F87" s="12">
-        <v>2113</v>
+        <v>1254</v>
       </c>
       <c r="G87" s="13" t="s">
         <v>36</v>
@@ -3651,13 +4227,13 @@
     </row>
     <row r="88" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>201</v>
+        <v>158</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D88" s="11" t="s">
         <v>35</v>
@@ -3666,7 +4242,7 @@
         <v>35</v>
       </c>
       <c r="F88" s="12">
-        <v>5129</v>
+        <v>1256</v>
       </c>
       <c r="G88" s="13" t="s">
         <v>36</v>
@@ -3677,13 +4253,13 @@
     </row>
     <row r="89" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>218</v>
+        <v>158</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D89" s="11" t="s">
         <v>35</v>
@@ -3692,7 +4268,7 @@
         <v>35</v>
       </c>
       <c r="F89" s="12">
-        <v>303</v>
+        <v>77</v>
       </c>
       <c r="G89" s="13" t="s">
         <v>36</v>
@@ -3703,13 +4279,13 @@
     </row>
     <row r="90" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>218</v>
+        <v>158</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D90" s="11" t="s">
         <v>35</v>
@@ -3718,7 +4294,7 @@
         <v>35</v>
       </c>
       <c r="F90" s="12">
-        <v>2604</v>
+        <v>84</v>
       </c>
       <c r="G90" s="13" t="s">
         <v>36</v>
@@ -3729,13 +4305,13 @@
     </row>
     <row r="91" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>218</v>
+        <v>158</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D91" s="11" t="s">
         <v>35</v>
@@ -3744,7 +4320,7 @@
         <v>35</v>
       </c>
       <c r="F91" s="12">
-        <v>2453</v>
+        <v>86</v>
       </c>
       <c r="G91" s="13" t="s">
         <v>36</v>
@@ -3755,13 +4331,13 @@
     </row>
     <row r="92" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D92" s="11" t="s">
         <v>35</v>
@@ -3770,7 +4346,7 @@
         <v>35</v>
       </c>
       <c r="F92" s="12">
-        <v>1515</v>
+        <v>403</v>
       </c>
       <c r="G92" s="13" t="s">
         <v>36</v>
@@ -3781,13 +4357,13 @@
     </row>
     <row r="93" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D93" s="11" t="s">
         <v>35</v>
@@ -3796,7 +4372,7 @@
         <v>35</v>
       </c>
       <c r="F93" s="12">
-        <v>1302</v>
+        <v>37</v>
       </c>
       <c r="G93" s="13" t="s">
         <v>36</v>
@@ -3807,13 +4383,13 @@
     </row>
     <row r="94" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D94" s="11" t="s">
         <v>35</v>
@@ -3822,7 +4398,7 @@
         <v>35</v>
       </c>
       <c r="F94" s="12">
-        <v>829</v>
+        <v>45</v>
       </c>
       <c r="G94" s="13" t="s">
         <v>36</v>
@@ -3833,13 +4409,13 @@
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D95" s="11" t="s">
         <v>35</v>
@@ -3848,7 +4424,7 @@
         <v>35</v>
       </c>
       <c r="F95" s="12">
-        <v>10054</v>
+        <v>33</v>
       </c>
       <c r="G95" s="13" t="s">
         <v>36</v>
@@ -3859,13 +4435,13 @@
     </row>
     <row r="96" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D96" s="11" t="s">
         <v>35</v>
@@ -3874,7 +4450,7 @@
         <v>35</v>
       </c>
       <c r="F96" s="12">
-        <v>54</v>
+        <v>1616</v>
       </c>
       <c r="G96" s="13" t="s">
         <v>36</v>
@@ -3885,13 +4461,13 @@
     </row>
     <row r="97" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D97" s="11" t="s">
         <v>35</v>
@@ -3900,7 +4476,7 @@
         <v>35</v>
       </c>
       <c r="F97" s="12">
-        <v>1462</v>
+        <v>1138</v>
       </c>
       <c r="G97" s="13" t="s">
         <v>36</v>
@@ -3911,13 +4487,13 @@
     </row>
     <row r="98" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D98" s="11" t="s">
         <v>35</v>
@@ -3926,7 +4502,7 @@
         <v>35</v>
       </c>
       <c r="F98" s="12">
-        <v>2908</v>
+        <v>1254</v>
       </c>
       <c r="G98" s="13" t="s">
         <v>36</v>
@@ -3937,13 +4513,13 @@
     </row>
     <row r="99" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D99" s="11" t="s">
         <v>35</v>
@@ -3952,7 +4528,7 @@
         <v>35</v>
       </c>
       <c r="F99" s="12">
-        <v>6279</v>
+        <v>1142</v>
       </c>
       <c r="G99" s="13" t="s">
         <v>36</v>
@@ -3963,13 +4539,13 @@
     </row>
     <row r="100" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D100" s="11" t="s">
         <v>35</v>
@@ -3978,7 +4554,7 @@
         <v>35</v>
       </c>
       <c r="F100" s="12">
-        <v>2717</v>
+        <v>1084</v>
       </c>
       <c r="G100" s="13" t="s">
         <v>36</v>
@@ -3989,13 +4565,13 @@
     </row>
     <row r="101" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="D101" s="11" t="s">
         <v>35</v>
@@ -4004,7 +4580,7 @@
         <v>35</v>
       </c>
       <c r="F101" s="12">
-        <v>4518</v>
+        <v>14</v>
       </c>
       <c r="G101" s="13" t="s">
         <v>36</v>
@@ -4015,13 +4591,13 @@
     </row>
     <row r="102" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D102" s="11" t="s">
         <v>35</v>
@@ -4030,7 +4606,7 @@
         <v>35</v>
       </c>
       <c r="F102" s="12">
-        <v>508</v>
+        <v>14</v>
       </c>
       <c r="G102" s="13" t="s">
         <v>36</v>
@@ -4041,13 +4617,13 @@
     </row>
     <row r="103" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D103" s="11" t="s">
         <v>35</v>
@@ -4056,7 +4632,7 @@
         <v>35</v>
       </c>
       <c r="F103" s="12">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="G103" s="13" t="s">
         <v>36</v>
@@ -4067,13 +4643,13 @@
     </row>
     <row r="104" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D104" s="11" t="s">
         <v>35</v>
@@ -4082,7 +4658,7 @@
         <v>35</v>
       </c>
       <c r="F104" s="12">
-        <v>442</v>
+        <v>1089</v>
       </c>
       <c r="G104" s="13" t="s">
         <v>36</v>
@@ -4093,27 +4669,2523 @@
     </row>
     <row r="105" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D105" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F105" s="12">
+        <v>22</v>
+      </c>
+      <c r="G105" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H105" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="D106" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F106" s="12">
+        <v>13</v>
+      </c>
+      <c r="G106" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H106" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C107" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="B105" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="C105" s="5" t="s">
+      <c r="D107" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F107" s="12">
+        <v>382</v>
+      </c>
+      <c r="G107" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H107" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="D105" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E105" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F105" s="12">
-        <v>3307</v>
-      </c>
-      <c r="G105" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="H105" s="5" t="s">
+      <c r="B108" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="D108" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E108" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F108" s="12">
+        <v>1809</v>
+      </c>
+      <c r="G108" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H108" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="109" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D109" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E109" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F109" s="12">
+        <v>1580</v>
+      </c>
+      <c r="G109" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H109" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="110" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D110" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E110" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F110" s="12">
+        <v>1273</v>
+      </c>
+      <c r="G110" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H110" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="111" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D111" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F111" s="12">
+        <v>469</v>
+      </c>
+      <c r="G111" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H111" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="112" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D112" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E112" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F112" s="12">
+        <v>1605</v>
+      </c>
+      <c r="G112" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H112" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="113" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="D113" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E113" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F113" s="12">
+        <v>18</v>
+      </c>
+      <c r="G113" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H113" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="114" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="D114" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F114" s="12">
+        <v>40</v>
+      </c>
+      <c r="G114" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H114" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="115" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E115" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F115" s="12">
+        <v>1142</v>
+      </c>
+      <c r="G115" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H115" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="116" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E116" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F116" s="12">
+        <v>11</v>
+      </c>
+      <c r="G116" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H116" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="117" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="D117" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E117" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F117" s="12">
+        <v>12</v>
+      </c>
+      <c r="G117" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H117" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="118" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E118" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F118" s="12">
+        <v>34</v>
+      </c>
+      <c r="G118" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H118" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="119" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F119" s="12">
+        <v>13</v>
+      </c>
+      <c r="G119" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H119" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="120" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F120" s="12">
+        <v>81</v>
+      </c>
+      <c r="G120" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H120" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="121" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E121" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F121" s="12">
+        <v>9</v>
+      </c>
+      <c r="G121" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H121" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="122" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E122" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F122" s="12">
+        <v>394</v>
+      </c>
+      <c r="G122" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H122" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="123" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D123" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E123" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F123" s="12">
+        <v>77</v>
+      </c>
+      <c r="G123" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H123" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="124" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="D124" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E124" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F124" s="12">
+        <v>268</v>
+      </c>
+      <c r="G124" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H124" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="125" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="D125" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E125" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F125" s="12">
+        <v>1133</v>
+      </c>
+      <c r="G125" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H125" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="126" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D126" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E126" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F126" s="12">
+        <v>11267</v>
+      </c>
+      <c r="G126" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H126" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="127" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F127" s="12">
+        <v>17020</v>
+      </c>
+      <c r="G127" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H127" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="128" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D128" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E128" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F128" s="12">
+        <v>10007</v>
+      </c>
+      <c r="G128" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H128" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="129" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D129" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F129" s="12">
+        <v>10004</v>
+      </c>
+      <c r="G129" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H129" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="130" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="D130" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F130" s="12">
+        <v>25</v>
+      </c>
+      <c r="G130" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H130" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="131" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D131" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F131" s="12">
+        <v>9</v>
+      </c>
+      <c r="G131" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H131" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="132" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D132" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F132" s="12">
+        <v>1117</v>
+      </c>
+      <c r="G132" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H132" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="133" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="D133" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E133" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F133" s="12">
+        <v>1083</v>
+      </c>
+      <c r="G133" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H133" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="134" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="D134" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F134" s="12">
+        <v>7</v>
+      </c>
+      <c r="G134" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H134" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="135" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D135" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E135" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F135" s="12">
+        <v>9</v>
+      </c>
+      <c r="G135" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H135" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="136" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D136" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E136" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F136" s="12">
+        <v>8</v>
+      </c>
+      <c r="G136" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H136" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="137" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="D137" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E137" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F137" s="12">
+        <v>23</v>
+      </c>
+      <c r="G137" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H137" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="138" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="D138" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F138" s="12">
+        <v>174</v>
+      </c>
+      <c r="G138" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H138" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="139" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D139" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F139" s="12">
+        <v>695</v>
+      </c>
+      <c r="G139" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H139" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="140" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="D140" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E140" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F140" s="12">
+        <v>710</v>
+      </c>
+      <c r="G140" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H140" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="141" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="D141" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F141" s="12">
+        <v>27</v>
+      </c>
+      <c r="G141" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H141" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="142" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="D142" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F142" s="12">
+        <v>38</v>
+      </c>
+      <c r="G142" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H142" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="143" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="D143" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F143" s="12">
+        <v>790</v>
+      </c>
+      <c r="G143" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H143" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="144" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="D144" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E144" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F144" s="12">
+        <v>360</v>
+      </c>
+      <c r="G144" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H144" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="145" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="D145" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E145" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F145" s="12">
+        <v>23</v>
+      </c>
+      <c r="G145" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H145" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="146" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="D146" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E146" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F146" s="12">
+        <v>16</v>
+      </c>
+      <c r="G146" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H146" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="147" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="D147" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E147" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F147" s="12">
+        <v>23</v>
+      </c>
+      <c r="G147" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H147" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="148" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="D148" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E148" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F148" s="12">
+        <v>621</v>
+      </c>
+      <c r="G148" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H148" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="149" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="D149" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E149" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F149" s="12">
+        <v>18</v>
+      </c>
+      <c r="G149" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H149" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="150" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="D150" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F150" s="12">
+        <v>15</v>
+      </c>
+      <c r="G150" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H150" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="151" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="D151" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E151" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F151" s="12">
+        <v>16</v>
+      </c>
+      <c r="G151" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H151" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="152" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="D152" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E152" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F152" s="12">
+        <v>176</v>
+      </c>
+      <c r="G152" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H152" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="153" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="D153" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E153" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F153" s="12">
+        <v>2157</v>
+      </c>
+      <c r="G153" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H153" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="154" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="D154" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E154" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F154" s="12">
+        <v>489</v>
+      </c>
+      <c r="G154" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H154" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="155" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="D155" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E155" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F155" s="12">
+        <v>7337</v>
+      </c>
+      <c r="G155" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H155" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="156" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="D156" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E156" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F156" s="12">
+        <v>1511</v>
+      </c>
+      <c r="G156" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H156" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="157" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="D157" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E157" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F157" s="12">
+        <v>8778</v>
+      </c>
+      <c r="G157" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H157" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="158" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="D158" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E158" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F158" s="12">
+        <v>2118</v>
+      </c>
+      <c r="G158" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H158" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="159" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="D159" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E159" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F159" s="12">
+        <v>5162</v>
+      </c>
+      <c r="G159" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H159" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="160" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D160" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E160" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F160" s="12">
+        <v>2252</v>
+      </c>
+      <c r="G160" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H160" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="161" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="D161" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E161" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F161" s="12">
+        <v>30</v>
+      </c>
+      <c r="G161" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H161" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="162" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="D162" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E162" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F162" s="12">
+        <v>11</v>
+      </c>
+      <c r="G162" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H162" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="163" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="D163" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E163" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F163" s="12">
+        <v>33</v>
+      </c>
+      <c r="G163" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H163" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="164" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="D164" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E164" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F164" s="12">
+        <v>15</v>
+      </c>
+      <c r="G164" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H164" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="165" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="D165" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E165" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F165" s="12">
+        <v>2347</v>
+      </c>
+      <c r="G165" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H165" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="166" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="D166" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E166" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F166" s="12">
+        <v>32</v>
+      </c>
+      <c r="G166" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H166" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="167" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="D167" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E167" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F167" s="12">
+        <v>333</v>
+      </c>
+      <c r="G167" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H167" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="168" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="D168" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E168" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F168" s="12">
+        <v>2630</v>
+      </c>
+      <c r="G168" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H168" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="169" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="D169" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E169" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F169" s="12">
+        <v>2574</v>
+      </c>
+      <c r="G169" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H169" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="170" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="D170" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E170" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F170" s="12">
+        <v>1514</v>
+      </c>
+      <c r="G170" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H170" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="171" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="D171" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E171" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F171" s="12">
+        <v>1386</v>
+      </c>
+      <c r="G171" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H171" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="172" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="D172" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E172" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F172" s="12">
+        <v>878</v>
+      </c>
+      <c r="G172" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H172" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="173" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="D173" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E173" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F173" s="12">
+        <v>10060</v>
+      </c>
+      <c r="G173" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H173" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="174" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="D174" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E174" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F174" s="12">
+        <v>53</v>
+      </c>
+      <c r="G174" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H174" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="175" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="D175" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E175" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F175" s="12">
+        <v>1075</v>
+      </c>
+      <c r="G175" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H175" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="176" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D176" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E176" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F176" s="12">
+        <v>1057</v>
+      </c>
+      <c r="G176" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H176" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="177" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="D177" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E177" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F177" s="12">
+        <v>10026</v>
+      </c>
+      <c r="G177" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H177" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="178" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="D178" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E178" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F178" s="12">
+        <v>7</v>
+      </c>
+      <c r="G178" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H178" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="179" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="D179" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E179" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F179" s="12">
+        <v>69</v>
+      </c>
+      <c r="G179" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H179" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="180" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="D180" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E180" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F180" s="12">
+        <v>1112</v>
+      </c>
+      <c r="G180" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H180" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="181" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D181" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E181" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F181" s="12">
+        <v>1178</v>
+      </c>
+      <c r="G181" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H181" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="182" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="D182" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E182" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F182" s="12">
+        <v>1318</v>
+      </c>
+      <c r="G182" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H182" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="183" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="D183" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E183" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F183" s="12">
+        <v>3535</v>
+      </c>
+      <c r="G183" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H183" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="184" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="D184" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E184" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F184" s="12">
+        <v>6664</v>
+      </c>
+      <c r="G184" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H184" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="185" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="D185" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E185" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F185" s="12">
+        <v>2701</v>
+      </c>
+      <c r="G185" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H185" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="186" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="D186" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E186" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F186" s="12">
+        <v>4402</v>
+      </c>
+      <c r="G186" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H186" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="187" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D187" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E187" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F187" s="12">
+        <v>523</v>
+      </c>
+      <c r="G187" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H187" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="188" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="D188" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E188" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F188" s="12">
+        <v>186</v>
+      </c>
+      <c r="G188" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H188" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="189" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="D189" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E189" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F189" s="12">
+        <v>598</v>
+      </c>
+      <c r="G189" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H189" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="190" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="D190" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E190" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F190" s="12">
+        <v>3555</v>
+      </c>
+      <c r="G190" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H190" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="191" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D191" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E191" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F191" s="12">
+        <v>126</v>
+      </c>
+      <c r="G191" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H191" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="192" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="D192" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E192" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F192" s="12">
+        <v>14</v>
+      </c>
+      <c r="G192" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H192" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="193" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="D193" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E193" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F193" s="12">
+        <v>64</v>
+      </c>
+      <c r="G193" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H193" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="194" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="D194" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E194" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F194" s="12">
+        <v>70</v>
+      </c>
+      <c r="G194" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H194" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="195" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="D195" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E195" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F195" s="12">
+        <v>72</v>
+      </c>
+      <c r="G195" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H195" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="196" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="D196" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E196" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F196" s="12">
+        <v>84</v>
+      </c>
+      <c r="G196" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H196" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="197" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="D197" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E197" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F197" s="12">
+        <v>62</v>
+      </c>
+      <c r="G197" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H197" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="198" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="D198" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E198" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F198" s="12">
+        <v>14</v>
+      </c>
+      <c r="G198" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H198" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="199" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="D199" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E199" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F199" s="12">
+        <v>65</v>
+      </c>
+      <c r="G199" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H199" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="200" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="D200" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E200" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F200" s="12">
+        <v>14</v>
+      </c>
+      <c r="G200" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H200" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="201" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="D201" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E201" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F201" s="12">
+        <v>54</v>
+      </c>
+      <c r="G201" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H201" s="5" t="s">
         <v>23</v>
       </c>
     </row>

--- a/selenium-tests/reports/excel/report.xlsx
+++ b/selenium-tests/reports/excel/report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2572" uniqueCount="793">
   <si>
     <t>MedMonitor E2E Test Suite Summary</t>
   </si>
@@ -20,7 +20,7 @@
     <t>Report Generation Date:</t>
   </si>
   <si>
-    <t>20/6/2026, 6:21:28 pm</t>
+    <t>22/6/2026, 11:14:16 am</t>
   </si>
   <si>
     <t>Target Environment:</t>
@@ -80,7 +80,7 @@
     <t>Total Run Duration</t>
   </si>
   <si>
-    <t>464.10 seconds</t>
+    <t>417.24 seconds</t>
   </si>
   <si>
     <t/>
@@ -1713,6 +1713,684 @@
   </si>
   <si>
     <t>Verify that the Clinical Notes block is displayed</t>
+  </si>
+  <si>
+    <t>17. PATIENT DOCUMENT &amp; EXPORT AUDIT WORKFLOWS</t>
+  </si>
+  <si>
+    <t>Test 17.1</t>
+  </si>
+  <si>
+    <t>17. Patient Document &amp; Export Audit Workflows</t>
+  </si>
+  <si>
+    <t>Verify PDF export button layout matches design standards</t>
+  </si>
+  <si>
+    <t>Test 17.2</t>
+  </si>
+  <si>
+    <t>Ensure export settings display format options (PDF, Excel, JSON)</t>
+  </si>
+  <si>
+    <t>Test 17.3</t>
+  </si>
+  <si>
+    <t>Verify adherence percentage is visible in PDF export preview</t>
+  </si>
+  <si>
+    <t>Test 17.4</t>
+  </si>
+  <si>
+    <t>Verify compliance table columns: Date, Medicine, Status</t>
+  </si>
+  <si>
+    <t>Test 17.5</t>
+  </si>
+  <si>
+    <t>Verify print page layout hides sidebars and headers</t>
+  </si>
+  <si>
+    <t>Test 17.6</t>
+  </si>
+  <si>
+    <t>Verify range selector contains standard intervals (7 days, 30 days)</t>
+  </si>
+  <si>
+    <t>Test 17.7</t>
+  </si>
+  <si>
+    <t>Ensure CSV exporter contains correct column headers</t>
+  </si>
+  <si>
+    <t>Test 17.8</t>
+  </si>
+  <si>
+    <t>Verify patient metadata is included in the document header</t>
+  </si>
+  <si>
+    <t>Test 17.9</t>
+  </si>
+  <si>
+    <t>Check export preview loader is hidden after load</t>
+  </si>
+  <si>
+    <t>Test 17.10</t>
+  </si>
+  <si>
+    <t>Verify clinical notes attachment display layout</t>
+  </si>
+  <si>
+    <t>Test 17.11</t>
+  </si>
+  <si>
+    <t>Verify hospital signature field is visible on export mockups</t>
+  </si>
+  <si>
+    <t>Test 17.12</t>
+  </si>
+  <si>
+    <t>Verify medicine dosage information renders correctly in preview table</t>
+  </si>
+  <si>
+    <t>Test 17.13</t>
+  </si>
+  <si>
+    <t>Ensure print preview dialog does not crash the React router</t>
+  </si>
+  <si>
+    <t>Test 17.14</t>
+  </si>
+  <si>
+    <t>Verify caregiver authorization stamp container renders</t>
+  </si>
+  <si>
+    <t>Test 17.15</t>
+  </si>
+  <si>
+    <t>Verify export date range label displays selected interval</t>
+  </si>
+  <si>
+    <t>Test 17.16</t>
+  </si>
+  <si>
+    <t>Verify file download progress bar accessibility</t>
+  </si>
+  <si>
+    <t>Test 17.17</t>
+  </si>
+  <si>
+    <t>Ensure data export rejects invalid custom date ranges</t>
+  </si>
+  <si>
+    <t>Test 17.18</t>
+  </si>
+  <si>
+    <t>Verify compliance summary widget layout in document body</t>
+  </si>
+  <si>
+    <t>Test 17.19</t>
+  </si>
+  <si>
+    <t>Verify medication history export limits match page settings</t>
+  </si>
+  <si>
+    <t>Test 17.20</t>
+  </si>
+  <si>
+    <t>Check page number indicators are visible on multi-page export views</t>
+  </si>
+  <si>
+    <t>Test 17.21</t>
+  </si>
+  <si>
+    <t>Verify that the clinic name is correctly printed on reports</t>
+  </si>
+  <si>
+    <t>Test 17.22</t>
+  </si>
+  <si>
+    <t>Verify table grid lines are enabled in Excel sheet preview</t>
+  </si>
+  <si>
+    <t>Test 17.23</t>
+  </si>
+  <si>
+    <t>Verify CSV download triggers a data structure check</t>
+  </si>
+  <si>
+    <t>Test 17.24</t>
+  </si>
+  <si>
+    <t>Ensure clinical summary table displays at least one record placeholder</t>
+  </si>
+  <si>
+    <t>Test 17.25</t>
+  </si>
+  <si>
+    <t>Verify page layout is set to portrait by default</t>
+  </si>
+  <si>
+    <t>Test 17.26</t>
+  </si>
+  <si>
+    <t>Check if signature line matches document footer placement</t>
+  </si>
+  <si>
+    <t>Test 17.27</t>
+  </si>
+  <si>
+    <t>Verify that the print button remains enabled on load</t>
+  </si>
+  <si>
+    <t>Test 17.28</t>
+  </si>
+  <si>
+    <t>Verify that downloading a reports bundle does not log out the user</t>
+  </si>
+  <si>
+    <t>Test 17.29</t>
+  </si>
+  <si>
+    <t>Ensure export data formatting handles special characters in medicine names</t>
+  </si>
+  <si>
+    <t>Test 17.30</t>
+  </si>
+  <si>
+    <t>Verify document checksum key layout is displayed in footer</t>
+  </si>
+  <si>
+    <t>18. CAREGIVER PATIENT MONITOR WORKFLOWS</t>
+  </si>
+  <si>
+    <t>Test 18.1</t>
+  </si>
+  <si>
+    <t>18. Caregiver Patient Monitor Workflows</t>
+  </si>
+  <si>
+    <t>Verify caregiver header panel component is loaded</t>
+  </si>
+  <si>
+    <t>Test 18.2</t>
+  </si>
+  <si>
+    <t>Ensure patient search form is rendered correctly</t>
+  </si>
+  <si>
+    <t>Test 18.3</t>
+  </si>
+  <si>
+    <t>Verify caregiver layout container has active sidebar</t>
+  </si>
+  <si>
+    <t>Test 18.4</t>
+  </si>
+  <si>
+    <t>Check caregiver assigned patients count badge is visible</t>
+  </si>
+  <si>
+    <t>Test 18.5</t>
+  </si>
+  <si>
+    <t>Verify patient metrics card layout displays patient list</t>
+  </si>
+  <si>
+    <t>Test 18.6</t>
+  </si>
+  <si>
+    <t>Check patient grid avatar thumbnail image rendering status</t>
+  </si>
+  <si>
+    <t>Test 18.7</t>
+  </si>
+  <si>
+    <t>Verify alert priority tags (High, Medium, Low) are colored correctly</t>
+  </si>
+  <si>
+    <t>Test 18.8</t>
+  </si>
+  <si>
+    <t>Verify critical condition cards apply flashing amber border style</t>
+  </si>
+  <si>
+    <t>Test 18.9</t>
+  </si>
+  <si>
+    <t>Ensure caregiver alerts queue sidebar displays latest updates</t>
+  </si>
+  <si>
+    <t>Test 18.10</t>
+  </si>
+  <si>
+    <t>Verify caregiver cross-patient comparison chart container is rendered</t>
+  </si>
+  <si>
+    <t>Test 18.11</t>
+  </si>
+  <si>
+    <t>Check caregiver wide system alert logs table is visible</t>
+  </si>
+  <si>
+    <t>Test 18.12</t>
+  </si>
+  <si>
+    <t>Ensure filter dropdown matches the current patients list classification</t>
+  </si>
+  <si>
+    <t>Test 18.13</t>
+  </si>
+  <si>
+    <t>Verify caregiver add patient button is visible on layout header</t>
+  </si>
+  <si>
+    <t>Test 18.14</t>
+  </si>
+  <si>
+    <t>Check patient medical ID search input container render</t>
+  </si>
+  <si>
+    <t>Test 18.15</t>
+  </si>
+  <si>
+    <t>Verify invite member button is accessible in circle page</t>
+  </si>
+  <si>
+    <t>Test 18.16</t>
+  </si>
+  <si>
+    <t>Ensure caregiver professional license code is displayed on profile page</t>
+  </si>
+  <si>
+    <t>Test 18.17</t>
+  </si>
+  <si>
+    <t>Verify caregiver clinics details info block is visible</t>
+  </si>
+  <si>
+    <t>Test 18.18</t>
+  </si>
+  <si>
+    <t>Ensure shift work schedule calendar grid loads without error</t>
+  </si>
+  <si>
+    <t>Test 18.19</t>
+  </si>
+  <si>
+    <t>Verify audio alert settings option is toggleable on sidebar</t>
+  </si>
+  <si>
+    <t>Test 18.20</t>
+  </si>
+  <si>
+    <t>Verify caregiver reports page display structure matches patients list</t>
+  </si>
+  <si>
+    <t>Test 18.21</t>
+  </si>
+  <si>
+    <t>Verify patient clinical details logs grid load latency indicator</t>
+  </si>
+  <si>
+    <t>Test 18.22</t>
+  </si>
+  <si>
+    <t>Ensure rich text doctor notes history editor renders correctly</t>
+  </si>
+  <si>
+    <t>Test 18.23</t>
+  </si>
+  <si>
+    <t>Verify caregiver risk assessment score color scales appropriately</t>
+  </si>
+  <si>
+    <t>Test 18.24</t>
+  </si>
+  <si>
+    <t>Ensure patient treatment plan action form container is visible</t>
+  </si>
+  <si>
+    <t>Test 18.25</t>
+  </si>
+  <si>
+    <t>Verify caregiver SMS escalation contact fields are visible</t>
+  </si>
+  <si>
+    <t>Test 18.26</t>
+  </si>
+  <si>
+    <t>Check caregiver hospital portal database connectivity status badge</t>
+  </si>
+  <si>
+    <t>Test 18.27</t>
+  </si>
+  <si>
+    <t>Verify that the active caregiver profile save updates indicator is hidden on load</t>
+  </si>
+  <si>
+    <t>Test 18.28</t>
+  </si>
+  <si>
+    <t>Verify caregiver layout navigation tabs contain link to Analytics page</t>
+  </si>
+  <si>
+    <t>Test 18.29</t>
+  </si>
+  <si>
+    <t>Ensure caregiver patient dashboard displays daily vitals check-in summaries</t>
+  </si>
+  <si>
+    <t>Test 18.30</t>
+  </si>
+  <si>
+    <t>Check caregiver active patient allergy list grid layout</t>
+  </si>
+  <si>
+    <t>Test 18.31</t>
+  </si>
+  <si>
+    <t>Verify caregiver patient immunization checklist component is rendered</t>
+  </si>
+  <si>
+    <t>Test 18.32</t>
+  </si>
+  <si>
+    <t>Verify caregiver patient prescription history table loads</t>
+  </si>
+  <si>
+    <t>Test 18.33</t>
+  </si>
+  <si>
+    <t>Ensure caregiver patient lab reports download button contains icon link</t>
+  </si>
+  <si>
+    <t>Test 18.34</t>
+  </si>
+  <si>
+    <t>Verify patient emergency contact card info displays layout spacing</t>
+  </si>
+  <si>
+    <t>Test 18.35</t>
+  </si>
+  <si>
+    <t>Verify active care circle members display avatars in caregivers detail page</t>
+  </si>
+  <si>
+    <t>Test 18.36</t>
+  </si>
+  <si>
+    <t>Ensure patient details prescription log container loading indicator clears</t>
+  </si>
+  <si>
+    <t>Test 18.37</t>
+  </si>
+  <si>
+    <t>Verify that caregiver navigation menu collapses to icon-only state correctly</t>
+  </si>
+  <si>
+    <t>Test 18.38</t>
+  </si>
+  <si>
+    <t>Verify that caregiver profile edit inputs block invalid clinic key input</t>
+  </si>
+  <si>
+    <t>Test 18.39</t>
+  </si>
+  <si>
+    <t>Ensure patient details vital signs graph container is visible on details view</t>
+  </si>
+  <si>
+    <t>Test 18.40</t>
+  </si>
+  <si>
+    <t>Verify that caregiver system configuration is readable on settings view</t>
+  </si>
+  <si>
+    <t>19. LOCAL CACHE &amp; SESSION STORAGE E2E VERIFICATION</t>
+  </si>
+  <si>
+    <t>Test 19.1</t>
+  </si>
+  <si>
+    <t>19. Local Cache &amp; Session Storage E2E Verification</t>
+  </si>
+  <si>
+    <t>Verify that LocalStorage read preferences matches theme default</t>
+  </si>
+  <si>
+    <t>Test 19.2</t>
+  </si>
+  <si>
+    <t>Ensure SessionStorage clean up is executed on tab logout link click</t>
+  </si>
+  <si>
+    <t>Test 19.3</t>
+  </si>
+  <si>
+    <t>Verify IndexedDB schema references are created during app initialization</t>
+  </si>
+  <si>
+    <t>Test 19.4</t>
+  </si>
+  <si>
+    <t>Verify local cache key for offline alerts sync buffer contains array data</t>
+  </si>
+  <si>
+    <t>Test 19.5</t>
+  </si>
+  <si>
+    <t>Verify user theme preference state persists inside LocalStorage keys</t>
+  </si>
+  <si>
+    <t>Test 19.6</t>
+  </si>
+  <si>
+    <t>Check authentication session cookie config checks for Secure attributes</t>
+  </si>
+  <si>
+    <t>Test 19.7</t>
+  </si>
+  <si>
+    <t>Verify offline analytics data is synchronized with backend once online</t>
+  </si>
+  <si>
+    <t>Test 19.8</t>
+  </si>
+  <si>
+    <t>Verify layout config overrides read from localStorage on view settle</t>
+  </si>
+  <si>
+    <t>Test 19.9</t>
+  </si>
+  <si>
+    <t>Check patient profile updates cache draft exists on active form</t>
+  </si>
+  <si>
+    <t>Test 19.10</t>
+  </si>
+  <si>
+    <t>Ensure local cache token expiry timers are initialized correctly</t>
+  </si>
+  <si>
+    <t>Test 19.11</t>
+  </si>
+  <si>
+    <t>Verify Firebase cache offline index configurations render correctly</t>
+  </si>
+  <si>
+    <t>Test 19.12</t>
+  </si>
+  <si>
+    <t>Verify caregiver patient search list is cached locally to support autocomplete</t>
+  </si>
+  <si>
+    <t>Test 19.13</t>
+  </si>
+  <si>
+    <t>Ensure cookie expiration dates are set within valid sessions duration limits</t>
+  </si>
+  <si>
+    <t>Test 19.14</t>
+  </si>
+  <si>
+    <t>Check that app settings sound level setting is retrieved from storage</t>
+  </si>
+  <si>
+    <t>Test 19.15</t>
+  </si>
+  <si>
+    <t>Verify cache size does not exceed system limit on continuous logging</t>
+  </si>
+  <si>
+    <t>Test 19.16</t>
+  </si>
+  <si>
+    <t>Verify that patient layout retrieves dashboard cached models</t>
+  </si>
+  <si>
+    <t>Test 19.17</t>
+  </si>
+  <si>
+    <t>Ensure local DB migration schema matches application production release version</t>
+  </si>
+  <si>
+    <t>Test 19.18</t>
+  </si>
+  <si>
+    <t>Verify cache clears safely when clinic details change</t>
+  </si>
+  <si>
+    <t>Test 19.19</t>
+  </si>
+  <si>
+    <t>Verify storage availability check returns true for browser context</t>
+  </si>
+  <si>
+    <t>Test 19.20</t>
+  </si>
+  <si>
+    <t>Ensure that medicine list query updates local cache parameters</t>
+  </si>
+  <si>
+    <t>Test 19.21</t>
+  </si>
+  <si>
+    <t>Verify database caching options display correct status in settings</t>
+  </si>
+  <si>
+    <t>Test 19.22</t>
+  </si>
+  <si>
+    <t>Check if user permissions list storage structure is encrypted in memory</t>
+  </si>
+  <si>
+    <t>Test 19.23</t>
+  </si>
+  <si>
+    <t>Verify offline medication logs queue is stored locally</t>
+  </si>
+  <si>
+    <t>Test 19.24</t>
+  </si>
+  <si>
+    <t>Verify that device synchronization button updates cache sync flag</t>
+  </si>
+  <si>
+    <t>Test 19.25</t>
+  </si>
+  <si>
+    <t>Ensure session cookies are removed on terminate session clicks</t>
+  </si>
+  <si>
+    <t>Test 19.26</t>
+  </si>
+  <si>
+    <t>Verify active caregivers listing remains cached during navigation</t>
+  </si>
+  <si>
+    <t>Test 19.27</t>
+  </si>
+  <si>
+    <t>Check that the app theme dropdown renders selections matching cached state</t>
+  </si>
+  <si>
+    <t>Test 19.28</t>
+  </si>
+  <si>
+    <t>Verify language choice is retrieved from local storage files on load</t>
+  </si>
+  <si>
+    <t>Test 19.29</t>
+  </si>
+  <si>
+    <t>Verify that local storage keys do not collide with other modules</t>
+  </si>
+  <si>
+    <t>Test 19.30</t>
+  </si>
+  <si>
+    <t>Ensure application version metadata is cached in footers local state</t>
+  </si>
+  <si>
+    <t>Test 19.31</t>
+  </si>
+  <si>
+    <t>Verify dark mode state toggle reflects directly on active layout classes</t>
+  </si>
+  <si>
+    <t>Test 19.32</t>
+  </si>
+  <si>
+    <t>Verify patient emergency SMS contacts cache structure is valid JSON</t>
+  </si>
+  <si>
+    <t>Test 19.33</t>
+  </si>
+  <si>
+    <t>Ensure caregiver patient cards display cache avatars prior to loading</t>
+  </si>
+  <si>
+    <t>Test 19.34</t>
+  </si>
+  <si>
+    <t>Verify cache invalidation logic executes on database reset action</t>
+  </si>
+  <si>
+    <t>Test 19.35</t>
+  </si>
+  <si>
+    <t>Verify offline check-in form responses are queued in local cache storage</t>
+  </si>
+  <si>
+    <t>Test 19.36</t>
+  </si>
+  <si>
+    <t>Ensure caregiver active alert monitor state sync indicators are visible</t>
+  </si>
+  <si>
+    <t>Test 19.37</t>
+  </si>
+  <si>
+    <t>Verify that patient layout page loads do not cause local cache churn</t>
+  </si>
+  <si>
+    <t>Test 19.38</t>
+  </si>
+  <si>
+    <t>Verify that cached telemetry logs are uploaded periodically</t>
+  </si>
+  <si>
+    <t>Test 19.39</t>
+  </si>
+  <si>
+    <t>Ensure storage quota limits are monitored by the client runtime engine</t>
+  </si>
+  <si>
+    <t>Test 19.40</t>
+  </si>
+  <si>
+    <t>Verify patient heart rate data ranges local storage key structure</t>
   </si>
 </sst>
 </file>
@@ -2253,7 +2931,7 @@
         <v>10</v>
       </c>
       <c r="B8" s="6">
-        <v>250</v>
+        <v>360</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>11</v>
@@ -2264,7 +2942,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="6">
-        <v>250</v>
+        <v>360</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>13</v>
@@ -2325,7 +3003,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I267"/>
+  <dimension ref="A1:I380"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2400,7 +3078,7 @@
         <v>37</v>
       </c>
       <c r="G3" s="13">
-        <v>4032</v>
+        <v>3430</v>
       </c>
       <c r="H3" s="14" t="s">
         <v>38</v>
@@ -2429,7 +3107,7 @@
         <v>37</v>
       </c>
       <c r="G4" s="13">
-        <v>2010</v>
+        <v>12895</v>
       </c>
       <c r="H4" s="14" t="s">
         <v>38</v>
@@ -2458,7 +3136,7 @@
         <v>37</v>
       </c>
       <c r="G5" s="13">
-        <v>465</v>
+        <v>933</v>
       </c>
       <c r="H5" s="14" t="s">
         <v>38</v>
@@ -2487,7 +3165,7 @@
         <v>37</v>
       </c>
       <c r="G6" s="13">
-        <v>2931</v>
+        <v>10390</v>
       </c>
       <c r="H6" s="14" t="s">
         <v>38</v>
@@ -2516,7 +3194,7 @@
         <v>37</v>
       </c>
       <c r="G7" s="13">
-        <v>1406</v>
+        <v>10312</v>
       </c>
       <c r="H7" s="14" t="s">
         <v>38</v>
@@ -2545,7 +3223,7 @@
         <v>37</v>
       </c>
       <c r="G8" s="13">
-        <v>2924</v>
+        <v>9507</v>
       </c>
       <c r="H8" s="14" t="s">
         <v>38</v>
@@ -2574,7 +3252,7 @@
         <v>37</v>
       </c>
       <c r="G9" s="13">
-        <v>2527</v>
+        <v>3564</v>
       </c>
       <c r="H9" s="14" t="s">
         <v>38</v>
@@ -2603,7 +3281,7 @@
         <v>37</v>
       </c>
       <c r="G10" s="13">
-        <v>1551</v>
+        <v>1743</v>
       </c>
       <c r="H10" s="14" t="s">
         <v>38</v>
@@ -2632,7 +3310,7 @@
         <v>37</v>
       </c>
       <c r="G11" s="13">
-        <v>5339</v>
+        <v>5548</v>
       </c>
       <c r="H11" s="14" t="s">
         <v>38</v>
@@ -2661,7 +3339,7 @@
         <v>37</v>
       </c>
       <c r="G12" s="13">
-        <v>1290</v>
+        <v>1253</v>
       </c>
       <c r="H12" s="14" t="s">
         <v>38</v>
@@ -2690,7 +3368,7 @@
         <v>37</v>
       </c>
       <c r="G13" s="13">
-        <v>10193</v>
+        <v>10261</v>
       </c>
       <c r="H13" s="14" t="s">
         <v>38</v>
@@ -2719,7 +3397,7 @@
         <v>37</v>
       </c>
       <c r="G14" s="13">
-        <v>10416</v>
+        <v>10399</v>
       </c>
       <c r="H14" s="14" t="s">
         <v>38</v>
@@ -2748,7 +3426,7 @@
         <v>37</v>
       </c>
       <c r="G15" s="13">
-        <v>147</v>
+        <v>371</v>
       </c>
       <c r="H15" s="14" t="s">
         <v>38</v>
@@ -2777,7 +3455,7 @@
         <v>37</v>
       </c>
       <c r="G16" s="13">
-        <v>10110</v>
+        <v>10222</v>
       </c>
       <c r="H16" s="14" t="s">
         <v>38</v>
@@ -2806,7 +3484,7 @@
         <v>37</v>
       </c>
       <c r="G17" s="13">
-        <v>10297</v>
+        <v>10270</v>
       </c>
       <c r="H17" s="14" t="s">
         <v>38</v>
@@ -2835,7 +3513,7 @@
         <v>37</v>
       </c>
       <c r="G18" s="13">
-        <v>10174</v>
+        <v>10191</v>
       </c>
       <c r="H18" s="14" t="s">
         <v>38</v>
@@ -2864,7 +3542,7 @@
         <v>37</v>
       </c>
       <c r="G19" s="13">
-        <v>10213</v>
+        <v>10355</v>
       </c>
       <c r="H19" s="14" t="s">
         <v>38</v>
@@ -2893,7 +3571,7 @@
         <v>37</v>
       </c>
       <c r="G20" s="13">
-        <v>10216</v>
+        <v>10332</v>
       </c>
       <c r="H20" s="14" t="s">
         <v>38</v>
@@ -2922,7 +3600,7 @@
         <v>37</v>
       </c>
       <c r="G21" s="13">
-        <v>186</v>
+        <v>129</v>
       </c>
       <c r="H21" s="14" t="s">
         <v>38</v>
@@ -2951,7 +3629,7 @@
         <v>37</v>
       </c>
       <c r="G22" s="13">
-        <v>10246</v>
+        <v>10078</v>
       </c>
       <c r="H22" s="14" t="s">
         <v>38</v>
@@ -2993,7 +3671,7 @@
         <v>37</v>
       </c>
       <c r="G24" s="13">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="H24" s="14" t="s">
         <v>38</v>
@@ -3022,7 +3700,7 @@
         <v>37</v>
       </c>
       <c r="G25" s="13">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H25" s="14" t="s">
         <v>38</v>
@@ -3051,7 +3729,7 @@
         <v>37</v>
       </c>
       <c r="G26" s="13">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H26" s="14" t="s">
         <v>38</v>
@@ -3080,7 +3758,7 @@
         <v>37</v>
       </c>
       <c r="G27" s="13">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="H27" s="14" t="s">
         <v>38</v>
@@ -3109,7 +3787,7 @@
         <v>37</v>
       </c>
       <c r="G28" s="13">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="H28" s="14" t="s">
         <v>38</v>
@@ -3138,7 +3816,7 @@
         <v>37</v>
       </c>
       <c r="G29" s="13">
-        <v>219</v>
+        <v>171</v>
       </c>
       <c r="H29" s="14" t="s">
         <v>38</v>
@@ -3167,7 +3845,7 @@
         <v>37</v>
       </c>
       <c r="G30" s="13">
-        <v>180</v>
+        <v>283</v>
       </c>
       <c r="H30" s="14" t="s">
         <v>38</v>
@@ -3196,7 +3874,7 @@
         <v>37</v>
       </c>
       <c r="G31" s="13">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="H31" s="14" t="s">
         <v>38</v>
@@ -3225,7 +3903,7 @@
         <v>37</v>
       </c>
       <c r="G32" s="13">
-        <v>1279</v>
+        <v>1088</v>
       </c>
       <c r="H32" s="14" t="s">
         <v>38</v>
@@ -3254,7 +3932,7 @@
         <v>37</v>
       </c>
       <c r="G33" s="13">
-        <v>352</v>
+        <v>430</v>
       </c>
       <c r="H33" s="14" t="s">
         <v>38</v>
@@ -3283,7 +3961,7 @@
         <v>37</v>
       </c>
       <c r="G34" s="13">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H34" s="14" t="s">
         <v>38</v>
@@ -3312,7 +3990,7 @@
         <v>37</v>
       </c>
       <c r="G35" s="13">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H35" s="14" t="s">
         <v>38</v>
@@ -3341,7 +4019,7 @@
         <v>37</v>
       </c>
       <c r="G36" s="13">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H36" s="14" t="s">
         <v>38</v>
@@ -3370,7 +4048,7 @@
         <v>37</v>
       </c>
       <c r="G37" s="13">
-        <v>617</v>
+        <v>597</v>
       </c>
       <c r="H37" s="14" t="s">
         <v>38</v>
@@ -3399,7 +4077,7 @@
         <v>37</v>
       </c>
       <c r="G38" s="13">
-        <v>1194</v>
+        <v>1433</v>
       </c>
       <c r="H38" s="14" t="s">
         <v>38</v>
@@ -3428,7 +4106,7 @@
         <v>37</v>
       </c>
       <c r="G39" s="13">
-        <v>222</v>
+        <v>110</v>
       </c>
       <c r="H39" s="14" t="s">
         <v>38</v>
@@ -3457,7 +4135,7 @@
         <v>37</v>
       </c>
       <c r="G40" s="13">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H40" s="14" t="s">
         <v>38</v>
@@ -3486,7 +4164,7 @@
         <v>37</v>
       </c>
       <c r="G41" s="13">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="H41" s="14" t="s">
         <v>38</v>
@@ -3515,7 +4193,7 @@
         <v>37</v>
       </c>
       <c r="G42" s="13">
-        <v>738</v>
+        <v>760</v>
       </c>
       <c r="H42" s="14" t="s">
         <v>38</v>
@@ -3544,7 +4222,7 @@
         <v>37</v>
       </c>
       <c r="G43" s="13">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="H43" s="14" t="s">
         <v>38</v>
@@ -3586,7 +4264,7 @@
         <v>37</v>
       </c>
       <c r="G45" s="13">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H45" s="14" t="s">
         <v>38</v>
@@ -3615,7 +4293,7 @@
         <v>37</v>
       </c>
       <c r="G46" s="13">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="H46" s="14" t="s">
         <v>38</v>
@@ -3644,7 +4322,7 @@
         <v>37</v>
       </c>
       <c r="G47" s="13">
-        <v>10086</v>
+        <v>39</v>
       </c>
       <c r="H47" s="14" t="s">
         <v>38</v>
@@ -3673,7 +4351,7 @@
         <v>37</v>
       </c>
       <c r="G48" s="13">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H48" s="14" t="s">
         <v>38</v>
@@ -3702,7 +4380,7 @@
         <v>37</v>
       </c>
       <c r="G49" s="13">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H49" s="14" t="s">
         <v>38</v>
@@ -3731,7 +4409,7 @@
         <v>37</v>
       </c>
       <c r="G50" s="13">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H50" s="14" t="s">
         <v>38</v>
@@ -3760,7 +4438,7 @@
         <v>37</v>
       </c>
       <c r="G51" s="13">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H51" s="14" t="s">
         <v>38</v>
@@ -3789,7 +4467,7 @@
         <v>37</v>
       </c>
       <c r="G52" s="13">
-        <v>15342</v>
+        <v>4045</v>
       </c>
       <c r="H52" s="14" t="s">
         <v>38</v>
@@ -3818,7 +4496,7 @@
         <v>37</v>
       </c>
       <c r="G53" s="13">
-        <v>10053</v>
+        <v>40</v>
       </c>
       <c r="H53" s="14" t="s">
         <v>38</v>
@@ -3847,7 +4525,7 @@
         <v>37</v>
       </c>
       <c r="G54" s="13">
-        <v>10074</v>
+        <v>23</v>
       </c>
       <c r="H54" s="14" t="s">
         <v>38</v>
@@ -3876,7 +4554,7 @@
         <v>37</v>
       </c>
       <c r="G55" s="13">
-        <v>10241</v>
+        <v>964</v>
       </c>
       <c r="H55" s="14" t="s">
         <v>38</v>
@@ -3905,7 +4583,7 @@
         <v>37</v>
       </c>
       <c r="G56" s="13">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H56" s="14" t="s">
         <v>38</v>
@@ -3934,7 +4612,7 @@
         <v>37</v>
       </c>
       <c r="G57" s="13">
-        <v>10027</v>
+        <v>240</v>
       </c>
       <c r="H57" s="14" t="s">
         <v>38</v>
@@ -3963,7 +4641,7 @@
         <v>37</v>
       </c>
       <c r="G58" s="13">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H58" s="14" t="s">
         <v>38</v>
@@ -3992,7 +4670,7 @@
         <v>37</v>
       </c>
       <c r="G59" s="13">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H59" s="14" t="s">
         <v>38</v>
@@ -4021,7 +4699,7 @@
         <v>37</v>
       </c>
       <c r="G60" s="13">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H60" s="14" t="s">
         <v>38</v>
@@ -4050,7 +4728,7 @@
         <v>37</v>
       </c>
       <c r="G61" s="13">
-        <v>10341</v>
+        <v>678</v>
       </c>
       <c r="H61" s="14" t="s">
         <v>38</v>
@@ -4079,7 +4757,7 @@
         <v>37</v>
       </c>
       <c r="G62" s="13">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="H62" s="14" t="s">
         <v>38</v>
@@ -4108,7 +4786,7 @@
         <v>37</v>
       </c>
       <c r="G63" s="13">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H63" s="14" t="s">
         <v>38</v>
@@ -4137,7 +4815,7 @@
         <v>37</v>
       </c>
       <c r="G64" s="13">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H64" s="14" t="s">
         <v>38</v>
@@ -4179,7 +4857,7 @@
         <v>37</v>
       </c>
       <c r="G66" s="13">
-        <v>284</v>
+        <v>147</v>
       </c>
       <c r="H66" s="14" t="s">
         <v>38</v>
@@ -4208,7 +4886,7 @@
         <v>37</v>
       </c>
       <c r="G67" s="13">
-        <v>1249</v>
+        <v>1173</v>
       </c>
       <c r="H67" s="14" t="s">
         <v>38</v>
@@ -4237,7 +4915,7 @@
         <v>37</v>
       </c>
       <c r="G68" s="13">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="H68" s="14" t="s">
         <v>38</v>
@@ -4266,7 +4944,7 @@
         <v>37</v>
       </c>
       <c r="G69" s="13">
-        <v>476</v>
+        <v>448</v>
       </c>
       <c r="H69" s="14" t="s">
         <v>38</v>
@@ -4295,7 +4973,7 @@
         <v>37</v>
       </c>
       <c r="G70" s="13">
-        <v>1205</v>
+        <v>1122</v>
       </c>
       <c r="H70" s="14" t="s">
         <v>38</v>
@@ -4324,7 +5002,7 @@
         <v>37</v>
       </c>
       <c r="G71" s="13">
-        <v>2936</v>
+        <v>2858</v>
       </c>
       <c r="H71" s="14" t="s">
         <v>38</v>
@@ -4353,7 +5031,7 @@
         <v>37</v>
       </c>
       <c r="G72" s="13">
-        <v>3244</v>
+        <v>3290</v>
       </c>
       <c r="H72" s="14" t="s">
         <v>38</v>
@@ -4382,7 +5060,7 @@
         <v>37</v>
       </c>
       <c r="G73" s="13">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="H73" s="14" t="s">
         <v>38</v>
@@ -4440,7 +5118,7 @@
         <v>37</v>
       </c>
       <c r="G75" s="13">
-        <v>4481</v>
+        <v>4551</v>
       </c>
       <c r="H75" s="14" t="s">
         <v>38</v>
@@ -4469,7 +5147,7 @@
         <v>37</v>
       </c>
       <c r="G76" s="13">
-        <v>3193</v>
+        <v>3245</v>
       </c>
       <c r="H76" s="14" t="s">
         <v>38</v>
@@ -4498,7 +5176,7 @@
         <v>37</v>
       </c>
       <c r="G77" s="13">
-        <v>1046</v>
+        <v>1098</v>
       </c>
       <c r="H77" s="14" t="s">
         <v>38</v>
@@ -4527,7 +5205,7 @@
         <v>37</v>
       </c>
       <c r="G78" s="13">
-        <v>4131</v>
+        <v>4135</v>
       </c>
       <c r="H78" s="14" t="s">
         <v>38</v>
@@ -4556,7 +5234,7 @@
         <v>37</v>
       </c>
       <c r="G79" s="13">
-        <v>17470</v>
+        <v>17474</v>
       </c>
       <c r="H79" s="14" t="s">
         <v>38</v>
@@ -4585,7 +5263,7 @@
         <v>37</v>
       </c>
       <c r="G80" s="13">
-        <v>2280</v>
+        <v>2284</v>
       </c>
       <c r="H80" s="14" t="s">
         <v>38</v>
@@ -4614,7 +5292,7 @@
         <v>37</v>
       </c>
       <c r="G81" s="13">
-        <v>5442</v>
+        <v>5494</v>
       </c>
       <c r="H81" s="14" t="s">
         <v>38</v>
@@ -4643,7 +5321,7 @@
         <v>37</v>
       </c>
       <c r="G82" s="13">
-        <v>8113</v>
+        <v>8092</v>
       </c>
       <c r="H82" s="14" t="s">
         <v>38</v>
@@ -4672,7 +5350,7 @@
         <v>37</v>
       </c>
       <c r="G83" s="13">
-        <v>13034</v>
+        <v>4688</v>
       </c>
       <c r="H83" s="14" t="s">
         <v>38</v>
@@ -4701,7 +5379,7 @@
         <v>37</v>
       </c>
       <c r="G84" s="13">
-        <v>2011</v>
+        <v>5114</v>
       </c>
       <c r="H84" s="14" t="s">
         <v>38</v>
@@ -4730,7 +5408,7 @@
         <v>37</v>
       </c>
       <c r="G85" s="13">
-        <v>13189</v>
+        <v>9477</v>
       </c>
       <c r="H85" s="14" t="s">
         <v>38</v>
@@ -4759,7 +5437,7 @@
         <v>37</v>
       </c>
       <c r="G86" s="13">
-        <v>11288</v>
+        <v>1696</v>
       </c>
       <c r="H86" s="14" t="s">
         <v>38</v>
@@ -4788,7 +5466,7 @@
         <v>37</v>
       </c>
       <c r="G87" s="13">
-        <v>1559</v>
+        <v>1289</v>
       </c>
       <c r="H87" s="14" t="s">
         <v>38</v>
@@ -4817,7 +5495,7 @@
         <v>37</v>
       </c>
       <c r="G88" s="13">
-        <v>1483</v>
+        <v>1239</v>
       </c>
       <c r="H88" s="14" t="s">
         <v>38</v>
@@ -4846,7 +5524,7 @@
         <v>37</v>
       </c>
       <c r="G89" s="13">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="H89" s="14" t="s">
         <v>38</v>
@@ -4875,7 +5553,7 @@
         <v>37</v>
       </c>
       <c r="G90" s="13">
-        <v>1247</v>
+        <v>1484</v>
       </c>
       <c r="H90" s="14" t="s">
         <v>38</v>
@@ -4904,7 +5582,7 @@
         <v>37</v>
       </c>
       <c r="G91" s="13">
-        <v>1229</v>
+        <v>1315</v>
       </c>
       <c r="H91" s="14" t="s">
         <v>38</v>
@@ -4933,7 +5611,7 @@
         <v>37</v>
       </c>
       <c r="G92" s="13">
-        <v>1305</v>
+        <v>1240</v>
       </c>
       <c r="H92" s="14" t="s">
         <v>38</v>
@@ -4962,7 +5640,7 @@
         <v>37</v>
       </c>
       <c r="G93" s="13">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="H93" s="14" t="s">
         <v>38</v>
@@ -4991,7 +5669,7 @@
         <v>37</v>
       </c>
       <c r="G94" s="13">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="H94" s="14" t="s">
         <v>38</v>
@@ -5020,7 +5698,7 @@
         <v>37</v>
       </c>
       <c r="G95" s="13">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="H95" s="14" t="s">
         <v>38</v>
@@ -5062,7 +5740,7 @@
         <v>37</v>
       </c>
       <c r="G97" s="13">
-        <v>385</v>
+        <v>600</v>
       </c>
       <c r="H97" s="14" t="s">
         <v>38</v>
@@ -5091,7 +5769,7 @@
         <v>37</v>
       </c>
       <c r="G98" s="13">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H98" s="14" t="s">
         <v>38</v>
@@ -5120,7 +5798,7 @@
         <v>37</v>
       </c>
       <c r="G99" s="13">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H99" s="14" t="s">
         <v>38</v>
@@ -5149,7 +5827,7 @@
         <v>37</v>
       </c>
       <c r="G100" s="13">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="H100" s="14" t="s">
         <v>38</v>
@@ -5178,7 +5856,7 @@
         <v>37</v>
       </c>
       <c r="G101" s="13">
-        <v>1655</v>
+        <v>1277</v>
       </c>
       <c r="H101" s="14" t="s">
         <v>38</v>
@@ -5207,7 +5885,7 @@
         <v>37</v>
       </c>
       <c r="G102" s="13">
-        <v>1149</v>
+        <v>1162</v>
       </c>
       <c r="H102" s="14" t="s">
         <v>38</v>
@@ -5236,7 +5914,7 @@
         <v>37</v>
       </c>
       <c r="G103" s="13">
-        <v>1196</v>
+        <v>1184</v>
       </c>
       <c r="H103" s="14" t="s">
         <v>38</v>
@@ -5265,7 +5943,7 @@
         <v>37</v>
       </c>
       <c r="G104" s="13">
-        <v>1239</v>
+        <v>1181</v>
       </c>
       <c r="H104" s="14" t="s">
         <v>38</v>
@@ -5294,7 +5972,7 @@
         <v>37</v>
       </c>
       <c r="G105" s="13">
-        <v>1101</v>
+        <v>1087</v>
       </c>
       <c r="H105" s="14" t="s">
         <v>38</v>
@@ -5323,7 +6001,7 @@
         <v>37</v>
       </c>
       <c r="G106" s="13">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H106" s="14" t="s">
         <v>38</v>
@@ -5352,7 +6030,7 @@
         <v>37</v>
       </c>
       <c r="G107" s="13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H107" s="14" t="s">
         <v>38</v>
@@ -5381,7 +6059,7 @@
         <v>37</v>
       </c>
       <c r="G108" s="13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H108" s="14" t="s">
         <v>38</v>
@@ -5410,7 +6088,7 @@
         <v>37</v>
       </c>
       <c r="G109" s="13">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="H109" s="14" t="s">
         <v>38</v>
@@ -5439,7 +6117,7 @@
         <v>37</v>
       </c>
       <c r="G110" s="13">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H110" s="14" t="s">
         <v>38</v>
@@ -5468,7 +6146,7 @@
         <v>37</v>
       </c>
       <c r="G111" s="13">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H111" s="14" t="s">
         <v>38</v>
@@ -5510,7 +6188,7 @@
         <v>37</v>
       </c>
       <c r="G113" s="13">
-        <v>483</v>
+        <v>533</v>
       </c>
       <c r="H113" s="14" t="s">
         <v>38</v>
@@ -5539,7 +6217,7 @@
         <v>37</v>
       </c>
       <c r="G114" s="13">
-        <v>1799</v>
+        <v>1588</v>
       </c>
       <c r="H114" s="14" t="s">
         <v>38</v>
@@ -5568,7 +6246,7 @@
         <v>37</v>
       </c>
       <c r="G115" s="13">
-        <v>1572</v>
+        <v>1563</v>
       </c>
       <c r="H115" s="14" t="s">
         <v>38</v>
@@ -5597,7 +6275,7 @@
         <v>37</v>
       </c>
       <c r="G116" s="13">
-        <v>1409</v>
+        <v>1257</v>
       </c>
       <c r="H116" s="14" t="s">
         <v>38</v>
@@ -5626,7 +6304,7 @@
         <v>37</v>
       </c>
       <c r="G117" s="13">
-        <v>525</v>
+        <v>295</v>
       </c>
       <c r="H117" s="14" t="s">
         <v>38</v>
@@ -5655,7 +6333,7 @@
         <v>37</v>
       </c>
       <c r="G118" s="13">
-        <v>1669</v>
+        <v>1612</v>
       </c>
       <c r="H118" s="14" t="s">
         <v>38</v>
@@ -5684,7 +6362,7 @@
         <v>37</v>
       </c>
       <c r="G119" s="13">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H119" s="14" t="s">
         <v>38</v>
@@ -5713,7 +6391,7 @@
         <v>37</v>
       </c>
       <c r="G120" s="13">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H120" s="14" t="s">
         <v>38</v>
@@ -5742,7 +6420,7 @@
         <v>37</v>
       </c>
       <c r="G121" s="13">
-        <v>1113</v>
+        <v>1090</v>
       </c>
       <c r="H121" s="14" t="s">
         <v>38</v>
@@ -5771,7 +6449,7 @@
         <v>37</v>
       </c>
       <c r="G122" s="13">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H122" s="14" t="s">
         <v>38</v>
@@ -5800,7 +6478,7 @@
         <v>37</v>
       </c>
       <c r="G123" s="13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H123" s="14" t="s">
         <v>38</v>
@@ -5829,7 +6507,7 @@
         <v>37</v>
       </c>
       <c r="G124" s="13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H124" s="14" t="s">
         <v>38</v>
@@ -5887,7 +6565,7 @@
         <v>37</v>
       </c>
       <c r="G126" s="13">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="H126" s="14" t="s">
         <v>38</v>
@@ -5958,7 +6636,7 @@
         <v>37</v>
       </c>
       <c r="G129" s="13">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H129" s="14" t="s">
         <v>38</v>
@@ -5987,7 +6665,7 @@
         <v>37</v>
       </c>
       <c r="G130" s="13">
-        <v>284</v>
+        <v>350</v>
       </c>
       <c r="H130" s="14" t="s">
         <v>38</v>
@@ -6016,7 +6694,7 @@
         <v>37</v>
       </c>
       <c r="G131" s="13">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H131" s="14" t="s">
         <v>38</v>
@@ -6045,7 +6723,7 @@
         <v>37</v>
       </c>
       <c r="G132" s="13">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="H132" s="14" t="s">
         <v>38</v>
@@ -6074,7 +6752,7 @@
         <v>37</v>
       </c>
       <c r="G133" s="13">
-        <v>11075</v>
+        <v>11179</v>
       </c>
       <c r="H133" s="14" t="s">
         <v>38</v>
@@ -6103,7 +6781,7 @@
         <v>37</v>
       </c>
       <c r="G134" s="13">
-        <v>17083</v>
+        <v>17218</v>
       </c>
       <c r="H134" s="14" t="s">
         <v>38</v>
@@ -6132,7 +6810,7 @@
         <v>37</v>
       </c>
       <c r="G135" s="13">
-        <v>10035</v>
+        <v>10215</v>
       </c>
       <c r="H135" s="14" t="s">
         <v>38</v>
@@ -6161,7 +6839,7 @@
         <v>37</v>
       </c>
       <c r="G136" s="13">
-        <v>10039</v>
+        <v>10025</v>
       </c>
       <c r="H136" s="14" t="s">
         <v>38</v>
@@ -6190,7 +6868,7 @@
         <v>37</v>
       </c>
       <c r="G137" s="13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H137" s="14" t="s">
         <v>38</v>
@@ -6219,7 +6897,7 @@
         <v>37</v>
       </c>
       <c r="G138" s="13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H138" s="14" t="s">
         <v>38</v>
@@ -6248,7 +6926,7 @@
         <v>37</v>
       </c>
       <c r="G139" s="13">
-        <v>1088</v>
+        <v>1079</v>
       </c>
       <c r="H139" s="14" t="s">
         <v>38</v>
@@ -6277,7 +6955,7 @@
         <v>37</v>
       </c>
       <c r="G140" s="13">
-        <v>1103</v>
+        <v>1070</v>
       </c>
       <c r="H140" s="14" t="s">
         <v>38</v>
@@ -6306,7 +6984,7 @@
         <v>37</v>
       </c>
       <c r="G141" s="13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H141" s="14" t="s">
         <v>38</v>
@@ -6335,7 +7013,7 @@
         <v>37</v>
       </c>
       <c r="G142" s="13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H142" s="14" t="s">
         <v>38</v>
@@ -6364,7 +7042,7 @@
         <v>37</v>
       </c>
       <c r="G143" s="13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H143" s="14" t="s">
         <v>38</v>
@@ -6406,7 +7084,7 @@
         <v>37</v>
       </c>
       <c r="G145" s="13">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H145" s="14" t="s">
         <v>38</v>
@@ -6435,7 +7113,7 @@
         <v>37</v>
       </c>
       <c r="G146" s="13">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="H146" s="14" t="s">
         <v>38</v>
@@ -6464,7 +7142,7 @@
         <v>37</v>
       </c>
       <c r="G147" s="13">
-        <v>770</v>
+        <v>700</v>
       </c>
       <c r="H147" s="14" t="s">
         <v>38</v>
@@ -6493,7 +7171,7 @@
         <v>37</v>
       </c>
       <c r="G148" s="13">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="H148" s="14" t="s">
         <v>38</v>
@@ -6522,7 +7200,7 @@
         <v>37</v>
       </c>
       <c r="G149" s="13">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H149" s="14" t="s">
         <v>38</v>
@@ -6551,7 +7229,7 @@
         <v>37</v>
       </c>
       <c r="G150" s="13">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="H150" s="14" t="s">
         <v>38</v>
@@ -6580,7 +7258,7 @@
         <v>37</v>
       </c>
       <c r="G151" s="13">
-        <v>750</v>
+        <v>718</v>
       </c>
       <c r="H151" s="14" t="s">
         <v>38</v>
@@ -6609,7 +7287,7 @@
         <v>37</v>
       </c>
       <c r="G152" s="13">
-        <v>572</v>
+        <v>516</v>
       </c>
       <c r="H152" s="14" t="s">
         <v>38</v>
@@ -6638,7 +7316,7 @@
         <v>37</v>
       </c>
       <c r="G153" s="13">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H153" s="14" t="s">
         <v>38</v>
@@ -6696,7 +7374,7 @@
         <v>37</v>
       </c>
       <c r="G155" s="13">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H155" s="14" t="s">
         <v>38</v>
@@ -6725,7 +7403,7 @@
         <v>37</v>
       </c>
       <c r="G156" s="13">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="H156" s="14" t="s">
         <v>38</v>
@@ -6754,7 +7432,7 @@
         <v>37</v>
       </c>
       <c r="G157" s="13">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H157" s="14" t="s">
         <v>38</v>
@@ -6783,7 +7461,7 @@
         <v>37</v>
       </c>
       <c r="G158" s="13">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H158" s="14" t="s">
         <v>38</v>
@@ -6812,7 +7490,7 @@
         <v>37</v>
       </c>
       <c r="G159" s="13">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H159" s="14" t="s">
         <v>38</v>
@@ -6854,7 +7532,7 @@
         <v>37</v>
       </c>
       <c r="G161" s="13">
-        <v>314</v>
+        <v>170</v>
       </c>
       <c r="H161" s="14" t="s">
         <v>38</v>
@@ -6883,7 +7561,7 @@
         <v>37</v>
       </c>
       <c r="G162" s="13">
-        <v>2122</v>
+        <v>2154</v>
       </c>
       <c r="H162" s="14" t="s">
         <v>38</v>
@@ -6912,7 +7590,7 @@
         <v>37</v>
       </c>
       <c r="G163" s="13">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="H163" s="14" t="s">
         <v>38</v>
@@ -6970,7 +7648,7 @@
         <v>37</v>
       </c>
       <c r="G165" s="13">
-        <v>1517</v>
+        <v>1508</v>
       </c>
       <c r="H165" s="14" t="s">
         <v>38</v>
@@ -6999,7 +7677,7 @@
         <v>37</v>
       </c>
       <c r="G166" s="13">
-        <v>8678</v>
+        <v>9148</v>
       </c>
       <c r="H166" s="14" t="s">
         <v>38</v>
@@ -7028,7 +7706,7 @@
         <v>37</v>
       </c>
       <c r="G167" s="13">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="H167" s="14" t="s">
         <v>38</v>
@@ -7057,7 +7735,7 @@
         <v>37</v>
       </c>
       <c r="G168" s="13">
-        <v>5231</v>
+        <v>5144</v>
       </c>
       <c r="H168" s="14" t="s">
         <v>38</v>
@@ -7086,7 +7764,7 @@
         <v>37</v>
       </c>
       <c r="G169" s="13">
-        <v>2237</v>
+        <v>2665</v>
       </c>
       <c r="H169" s="14" t="s">
         <v>38</v>
@@ -7144,7 +7822,7 @@
         <v>37</v>
       </c>
       <c r="G171" s="13">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H171" s="14" t="s">
         <v>38</v>
@@ -7173,7 +7851,7 @@
         <v>37</v>
       </c>
       <c r="G172" s="13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H172" s="14" t="s">
         <v>38</v>
@@ -7202,7 +7880,7 @@
         <v>37</v>
       </c>
       <c r="G173" s="13">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H173" s="14" t="s">
         <v>38</v>
@@ -7231,7 +7909,7 @@
         <v>37</v>
       </c>
       <c r="G174" s="13">
-        <v>2576</v>
+        <v>3846</v>
       </c>
       <c r="H174" s="14" t="s">
         <v>38</v>
@@ -7260,7 +7938,7 @@
         <v>37</v>
       </c>
       <c r="G175" s="13">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H175" s="14" t="s">
         <v>38</v>
@@ -7302,7 +7980,7 @@
         <v>37</v>
       </c>
       <c r="G177" s="13">
-        <v>164</v>
+        <v>285</v>
       </c>
       <c r="H177" s="14" t="s">
         <v>38</v>
@@ -7331,7 +8009,7 @@
         <v>37</v>
       </c>
       <c r="G178" s="13">
-        <v>2622</v>
+        <v>2607</v>
       </c>
       <c r="H178" s="14" t="s">
         <v>38</v>
@@ -7360,7 +8038,7 @@
         <v>37</v>
       </c>
       <c r="G179" s="13">
-        <v>2459</v>
+        <v>2631</v>
       </c>
       <c r="H179" s="14" t="s">
         <v>38</v>
@@ -7389,7 +8067,7 @@
         <v>37</v>
       </c>
       <c r="G180" s="13">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="H180" s="14" t="s">
         <v>38</v>
@@ -7418,7 +8096,7 @@
         <v>37</v>
       </c>
       <c r="G181" s="13">
-        <v>1401</v>
+        <v>1413</v>
       </c>
       <c r="H181" s="14" t="s">
         <v>38</v>
@@ -7447,7 +8125,7 @@
         <v>37</v>
       </c>
       <c r="G182" s="13">
-        <v>874</v>
+        <v>1248</v>
       </c>
       <c r="H182" s="14" t="s">
         <v>38</v>
@@ -7476,7 +8154,7 @@
         <v>37</v>
       </c>
       <c r="G183" s="13">
-        <v>10017</v>
+        <v>10012</v>
       </c>
       <c r="H183" s="14" t="s">
         <v>38</v>
@@ -7505,7 +8183,7 @@
         <v>37</v>
       </c>
       <c r="G184" s="13">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="H184" s="14" t="s">
         <v>38</v>
@@ -7534,7 +8212,7 @@
         <v>37</v>
       </c>
       <c r="G185" s="13">
-        <v>1056</v>
+        <v>1049</v>
       </c>
       <c r="H185" s="14" t="s">
         <v>38</v>
@@ -7563,7 +8241,7 @@
         <v>37</v>
       </c>
       <c r="G186" s="13">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H186" s="14" t="s">
         <v>38</v>
@@ -7592,7 +8270,7 @@
         <v>37</v>
       </c>
       <c r="G187" s="13">
-        <v>10029</v>
+        <v>10027</v>
       </c>
       <c r="H187" s="14" t="s">
         <v>38</v>
@@ -7679,7 +8357,7 @@
         <v>37</v>
       </c>
       <c r="G190" s="13">
-        <v>1134</v>
+        <v>1094</v>
       </c>
       <c r="H190" s="14" t="s">
         <v>38</v>
@@ -7708,7 +8386,7 @@
         <v>37</v>
       </c>
       <c r="G191" s="13">
-        <v>1099</v>
+        <v>1080</v>
       </c>
       <c r="H191" s="14" t="s">
         <v>38</v>
@@ -7750,7 +8428,7 @@
         <v>37</v>
       </c>
       <c r="G193" s="13">
-        <v>1109</v>
+        <v>1256</v>
       </c>
       <c r="H193" s="14" t="s">
         <v>38</v>
@@ -7779,7 +8457,7 @@
         <v>37</v>
       </c>
       <c r="G194" s="13">
-        <v>3037</v>
+        <v>3972</v>
       </c>
       <c r="H194" s="14" t="s">
         <v>38</v>
@@ -7808,7 +8486,7 @@
         <v>37</v>
       </c>
       <c r="G195" s="13">
-        <v>5635</v>
+        <v>6255</v>
       </c>
       <c r="H195" s="14" t="s">
         <v>38</v>
@@ -7837,7 +8515,7 @@
         <v>37</v>
       </c>
       <c r="G196" s="13">
-        <v>2990</v>
+        <v>2963</v>
       </c>
       <c r="H196" s="14" t="s">
         <v>38</v>
@@ -7866,7 +8544,7 @@
         <v>37</v>
       </c>
       <c r="G197" s="13">
-        <v>4149</v>
+        <v>4945</v>
       </c>
       <c r="H197" s="14" t="s">
         <v>38</v>
@@ -7895,7 +8573,7 @@
         <v>37</v>
       </c>
       <c r="G198" s="13">
-        <v>499</v>
+        <v>439</v>
       </c>
       <c r="H198" s="14" t="s">
         <v>38</v>
@@ -7924,7 +8602,7 @@
         <v>37</v>
       </c>
       <c r="G199" s="13">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="H199" s="14" t="s">
         <v>38</v>
@@ -7953,7 +8631,7 @@
         <v>37</v>
       </c>
       <c r="G200" s="13">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H200" s="14" t="s">
         <v>38</v>
@@ -7982,7 +8660,7 @@
         <v>37</v>
       </c>
       <c r="G201" s="13">
-        <v>3469</v>
+        <v>3542</v>
       </c>
       <c r="H201" s="14" t="s">
         <v>38</v>
@@ -8011,7 +8689,7 @@
         <v>37</v>
       </c>
       <c r="G202" s="13">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="H202" s="14" t="s">
         <v>38</v>
@@ -8040,7 +8718,7 @@
         <v>37</v>
       </c>
       <c r="G203" s="13">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="H203" s="14" t="s">
         <v>38</v>
@@ -8069,7 +8747,7 @@
         <v>37</v>
       </c>
       <c r="G204" s="13">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="H204" s="14" t="s">
         <v>38</v>
@@ -8098,7 +8776,7 @@
         <v>37</v>
       </c>
       <c r="G205" s="13">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="H205" s="14" t="s">
         <v>38</v>
@@ -8127,7 +8805,7 @@
         <v>37</v>
       </c>
       <c r="G206" s="13">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="H206" s="14" t="s">
         <v>38</v>
@@ -8156,7 +8834,7 @@
         <v>37</v>
       </c>
       <c r="G207" s="13">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="H207" s="14" t="s">
         <v>38</v>
@@ -8185,7 +8863,7 @@
         <v>37</v>
       </c>
       <c r="G208" s="13">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="H208" s="14" t="s">
         <v>38</v>
@@ -8214,7 +8892,7 @@
         <v>37</v>
       </c>
       <c r="G209" s="13">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="H209" s="14" t="s">
         <v>38</v>
@@ -8243,7 +8921,7 @@
         <v>37</v>
       </c>
       <c r="G210" s="13">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H210" s="14" t="s">
         <v>38</v>
@@ -8272,7 +8950,7 @@
         <v>37</v>
       </c>
       <c r="G211" s="13">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="H211" s="14" t="s">
         <v>38</v>
@@ -8301,7 +8979,7 @@
         <v>37</v>
       </c>
       <c r="G212" s="13">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H212" s="14" t="s">
         <v>38</v>
@@ -8343,7 +9021,7 @@
         <v>37</v>
       </c>
       <c r="G214" s="13">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="H214" s="14" t="s">
         <v>38</v>
@@ -8372,7 +9050,7 @@
         <v>37</v>
       </c>
       <c r="G215" s="13">
-        <v>562</v>
+        <v>487</v>
       </c>
       <c r="H215" s="14" t="s">
         <v>38</v>
@@ -8401,7 +9079,7 @@
         <v>37</v>
       </c>
       <c r="G216" s="13">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H216" s="14" t="s">
         <v>38</v>
@@ -8430,7 +9108,7 @@
         <v>37</v>
       </c>
       <c r="G217" s="13">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H217" s="14" t="s">
         <v>38</v>
@@ -8459,7 +9137,7 @@
         <v>37</v>
       </c>
       <c r="G218" s="13">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H218" s="14" t="s">
         <v>38</v>
@@ -8517,7 +9195,7 @@
         <v>37</v>
       </c>
       <c r="G220" s="13">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H220" s="14" t="s">
         <v>38</v>
@@ -8546,7 +9224,7 @@
         <v>37</v>
       </c>
       <c r="G221" s="13">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H221" s="14" t="s">
         <v>38</v>
@@ -8575,7 +9253,7 @@
         <v>37</v>
       </c>
       <c r="G222" s="13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H222" s="14" t="s">
         <v>38</v>
@@ -8604,7 +9282,7 @@
         <v>37</v>
       </c>
       <c r="G223" s="13">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H223" s="14" t="s">
         <v>38</v>
@@ -8646,7 +9324,7 @@
         <v>37</v>
       </c>
       <c r="G225" s="13">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H225" s="14" t="s">
         <v>38</v>
@@ -8675,7 +9353,7 @@
         <v>37</v>
       </c>
       <c r="G226" s="13">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="H226" s="14" t="s">
         <v>38</v>
@@ -8704,7 +9382,7 @@
         <v>37</v>
       </c>
       <c r="G227" s="13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H227" s="14" t="s">
         <v>38</v>
@@ -8733,7 +9411,7 @@
         <v>37</v>
       </c>
       <c r="G228" s="13">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H228" s="14" t="s">
         <v>38</v>
@@ -8762,7 +9440,7 @@
         <v>37</v>
       </c>
       <c r="G229" s="13">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H229" s="14" t="s">
         <v>38</v>
@@ -8791,7 +9469,7 @@
         <v>37</v>
       </c>
       <c r="G230" s="13">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H230" s="14" t="s">
         <v>38</v>
@@ -8820,7 +9498,7 @@
         <v>37</v>
       </c>
       <c r="G231" s="13">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H231" s="14" t="s">
         <v>38</v>
@@ -8849,7 +9527,7 @@
         <v>37</v>
       </c>
       <c r="G232" s="13">
-        <v>470</v>
+        <v>496</v>
       </c>
       <c r="H232" s="14" t="s">
         <v>38</v>
@@ -8878,7 +9556,7 @@
         <v>37</v>
       </c>
       <c r="G233" s="13">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H233" s="14" t="s">
         <v>38</v>
@@ -8907,7 +9585,7 @@
         <v>37</v>
       </c>
       <c r="G234" s="13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H234" s="14" t="s">
         <v>38</v>
@@ -8949,7 +9627,7 @@
         <v>37</v>
       </c>
       <c r="G236" s="13">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H236" s="14" t="s">
         <v>38</v>
@@ -8978,7 +9656,7 @@
         <v>37</v>
       </c>
       <c r="G237" s="13">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H237" s="14" t="s">
         <v>38</v>
@@ -9007,7 +9685,7 @@
         <v>37</v>
       </c>
       <c r="G238" s="13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H238" s="14" t="s">
         <v>38</v>
@@ -9036,7 +9714,7 @@
         <v>37</v>
       </c>
       <c r="G239" s="13">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H239" s="14" t="s">
         <v>38</v>
@@ -9094,7 +9772,7 @@
         <v>37</v>
       </c>
       <c r="G241" s="13">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H241" s="14" t="s">
         <v>38</v>
@@ -9123,7 +9801,7 @@
         <v>37</v>
       </c>
       <c r="G242" s="13">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H242" s="14" t="s">
         <v>38</v>
@@ -9152,7 +9830,7 @@
         <v>37</v>
       </c>
       <c r="G243" s="13">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H243" s="14" t="s">
         <v>38</v>
@@ -9181,7 +9859,7 @@
         <v>37</v>
       </c>
       <c r="G244" s="13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H244" s="14" t="s">
         <v>38</v>
@@ -9210,7 +9888,7 @@
         <v>37</v>
       </c>
       <c r="G245" s="13">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="H245" s="14" t="s">
         <v>38</v>
@@ -9252,7 +9930,7 @@
         <v>37</v>
       </c>
       <c r="G247" s="13">
-        <v>201</v>
+        <v>153</v>
       </c>
       <c r="H247" s="14" t="s">
         <v>38</v>
@@ -9281,7 +9959,7 @@
         <v>37</v>
       </c>
       <c r="G248" s="13">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H248" s="14" t="s">
         <v>38</v>
@@ -9339,7 +10017,7 @@
         <v>37</v>
       </c>
       <c r="G250" s="13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H250" s="14" t="s">
         <v>38</v>
@@ -9368,7 +10046,7 @@
         <v>37</v>
       </c>
       <c r="G251" s="13">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H251" s="14" t="s">
         <v>38</v>
@@ -9397,7 +10075,7 @@
         <v>37</v>
       </c>
       <c r="G252" s="13">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H252" s="14" t="s">
         <v>38</v>
@@ -9426,7 +10104,7 @@
         <v>37</v>
       </c>
       <c r="G253" s="13">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H253" s="14" t="s">
         <v>38</v>
@@ -9455,7 +10133,7 @@
         <v>37</v>
       </c>
       <c r="G254" s="13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H254" s="14" t="s">
         <v>38</v>
@@ -9484,7 +10162,7 @@
         <v>37</v>
       </c>
       <c r="G255" s="13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H255" s="14" t="s">
         <v>38</v>
@@ -9513,7 +10191,7 @@
         <v>37</v>
       </c>
       <c r="G256" s="13">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="H256" s="14" t="s">
         <v>38</v>
@@ -9555,7 +10233,7 @@
         <v>37</v>
       </c>
       <c r="G258" s="13">
-        <v>2443</v>
+        <v>2429</v>
       </c>
       <c r="H258" s="14" t="s">
         <v>38</v>
@@ -9584,7 +10262,7 @@
         <v>37</v>
       </c>
       <c r="G259" s="13">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H259" s="14" t="s">
         <v>38</v>
@@ -9613,7 +10291,7 @@
         <v>37</v>
       </c>
       <c r="G260" s="13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H260" s="14" t="s">
         <v>38</v>
@@ -9642,7 +10320,7 @@
         <v>37</v>
       </c>
       <c r="G261" s="13">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H261" s="14" t="s">
         <v>38</v>
@@ -9671,7 +10349,7 @@
         <v>37</v>
       </c>
       <c r="G262" s="13">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="H262" s="14" t="s">
         <v>38</v>
@@ -9700,7 +10378,7 @@
         <v>37</v>
       </c>
       <c r="G263" s="13">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="H263" s="14" t="s">
         <v>38</v>
@@ -9729,7 +10407,7 @@
         <v>37</v>
       </c>
       <c r="G264" s="13">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="H264" s="14" t="s">
         <v>38</v>
@@ -9787,7 +10465,7 @@
         <v>37</v>
       </c>
       <c r="G266" s="13">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H266" s="14" t="s">
         <v>38</v>
@@ -9825,8 +10503,3237 @@
         <v>23</v>
       </c>
     </row>
+    <row r="268" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A268" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="B268" s="11"/>
+      <c r="C268" s="11"/>
+      <c r="D268" s="11"/>
+      <c r="E268" s="11"/>
+      <c r="F268" s="11"/>
+      <c r="G268" s="11"/>
+      <c r="H268" s="11"/>
+      <c r="I268" s="11"/>
+    </row>
+    <row r="269" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A269" s="7">
+        <v>251</v>
+      </c>
+      <c r="B269" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="C269" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D269" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="E269" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F269" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G269" s="13">
+        <v>20</v>
+      </c>
+      <c r="H269" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I269" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="270" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A270" s="7">
+        <v>252</v>
+      </c>
+      <c r="B270" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="C270" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D270" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="E270" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F270" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G270" s="13">
+        <v>17</v>
+      </c>
+      <c r="H270" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I270" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="271" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A271" s="7">
+        <v>253</v>
+      </c>
+      <c r="B271" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="C271" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D271" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="E271" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F271" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G271" s="13">
+        <v>72</v>
+      </c>
+      <c r="H271" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I271" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="272" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A272" s="7">
+        <v>254</v>
+      </c>
+      <c r="B272" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="C272" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D272" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="E272" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F272" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G272" s="13">
+        <v>32</v>
+      </c>
+      <c r="H272" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I272" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="273" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A273" s="7">
+        <v>255</v>
+      </c>
+      <c r="B273" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="C273" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D273" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="E273" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F273" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G273" s="13">
+        <v>13</v>
+      </c>
+      <c r="H273" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I273" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="274" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A274" s="7">
+        <v>256</v>
+      </c>
+      <c r="B274" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="C274" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D274" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="E274" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F274" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G274" s="13">
+        <v>12</v>
+      </c>
+      <c r="H274" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I274" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="275" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A275" s="7">
+        <v>257</v>
+      </c>
+      <c r="B275" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="C275" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D275" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="E275" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F275" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G275" s="13">
+        <v>12</v>
+      </c>
+      <c r="H275" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I275" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="276" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A276" s="7">
+        <v>258</v>
+      </c>
+      <c r="B276" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="C276" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D276" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="E276" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F276" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G276" s="13">
+        <v>11</v>
+      </c>
+      <c r="H276" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I276" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="277" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A277" s="7">
+        <v>259</v>
+      </c>
+      <c r="B277" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="C277" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D277" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="E277" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F277" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G277" s="13">
+        <v>13</v>
+      </c>
+      <c r="H277" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I277" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="278" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A278" s="7">
+        <v>260</v>
+      </c>
+      <c r="B278" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="C278" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D278" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="E278" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F278" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G278" s="13">
+        <v>11</v>
+      </c>
+      <c r="H278" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I278" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="279" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A279" s="7">
+        <v>261</v>
+      </c>
+      <c r="B279" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="C279" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D279" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="E279" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F279" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G279" s="13">
+        <v>12</v>
+      </c>
+      <c r="H279" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I279" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="280" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A280" s="7">
+        <v>262</v>
+      </c>
+      <c r="B280" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="C280" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D280" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="E280" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F280" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G280" s="13">
+        <v>12</v>
+      </c>
+      <c r="H280" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I280" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="281" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A281" s="7">
+        <v>263</v>
+      </c>
+      <c r="B281" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="C281" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D281" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="E281" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F281" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G281" s="13">
+        <v>11</v>
+      </c>
+      <c r="H281" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I281" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="282" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A282" s="7">
+        <v>264</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="C282" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D282" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="E282" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F282" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G282" s="13">
+        <v>13</v>
+      </c>
+      <c r="H282" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I282" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="283" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A283" s="7">
+        <v>265</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="C283" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D283" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="E283" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F283" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G283" s="13">
+        <v>10</v>
+      </c>
+      <c r="H283" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I283" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="284" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A284" s="7">
+        <v>266</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="C284" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D284" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="E284" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F284" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G284" s="13">
+        <v>10</v>
+      </c>
+      <c r="H284" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I284" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="285" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A285" s="7">
+        <v>267</v>
+      </c>
+      <c r="B285" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="C285" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D285" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="E285" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F285" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G285" s="13">
+        <v>12</v>
+      </c>
+      <c r="H285" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I285" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="286" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A286" s="7">
+        <v>268</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="C286" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D286" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="E286" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F286" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G286" s="13">
+        <v>11</v>
+      </c>
+      <c r="H286" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I286" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="287" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A287" s="7">
+        <v>269</v>
+      </c>
+      <c r="B287" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="C287" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D287" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="E287" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F287" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G287" s="13">
+        <v>11</v>
+      </c>
+      <c r="H287" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I287" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="288" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A288" s="7">
+        <v>270</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="C288" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D288" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="E288" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F288" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G288" s="13">
+        <v>14</v>
+      </c>
+      <c r="H288" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I288" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="289" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A289" s="7">
+        <v>271</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="C289" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D289" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="E289" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F289" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G289" s="13">
+        <v>11</v>
+      </c>
+      <c r="H289" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I289" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="290" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A290" s="7">
+        <v>272</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="C290" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D290" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="E290" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F290" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G290" s="13">
+        <v>11</v>
+      </c>
+      <c r="H290" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I290" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="291" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A291" s="7">
+        <v>273</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C291" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D291" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="E291" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F291" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G291" s="13">
+        <v>14</v>
+      </c>
+      <c r="H291" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I291" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="292" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A292" s="7">
+        <v>274</v>
+      </c>
+      <c r="B292" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="C292" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D292" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="E292" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F292" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G292" s="13">
+        <v>14</v>
+      </c>
+      <c r="H292" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I292" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="293" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A293" s="7">
+        <v>275</v>
+      </c>
+      <c r="B293" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="C293" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D293" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="E293" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F293" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G293" s="13">
+        <v>13</v>
+      </c>
+      <c r="H293" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I293" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="294" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A294" s="7">
+        <v>276</v>
+      </c>
+      <c r="B294" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="C294" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D294" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="E294" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F294" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G294" s="13">
+        <v>11</v>
+      </c>
+      <c r="H294" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I294" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="295" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A295" s="7">
+        <v>277</v>
+      </c>
+      <c r="B295" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="C295" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D295" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="E295" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F295" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G295" s="13">
+        <v>12</v>
+      </c>
+      <c r="H295" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I295" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="296" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A296" s="7">
+        <v>278</v>
+      </c>
+      <c r="B296" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="C296" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D296" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="E296" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F296" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G296" s="13">
+        <v>11</v>
+      </c>
+      <c r="H296" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I296" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="297" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A297" s="7">
+        <v>279</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D297" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="E297" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F297" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G297" s="13">
+        <v>11</v>
+      </c>
+      <c r="H297" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I297" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="298" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A298" s="7">
+        <v>280</v>
+      </c>
+      <c r="B298" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="C298" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D298" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="E298" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F298" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G298" s="13">
+        <v>17</v>
+      </c>
+      <c r="H298" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I298" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="299" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A299" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="B299" s="11"/>
+      <c r="C299" s="11"/>
+      <c r="D299" s="11"/>
+      <c r="E299" s="11"/>
+      <c r="F299" s="11"/>
+      <c r="G299" s="11"/>
+      <c r="H299" s="11"/>
+      <c r="I299" s="11"/>
+    </row>
+    <row r="300" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A300" s="7">
+        <v>281</v>
+      </c>
+      <c r="B300" s="6" t="s">
+        <v>630</v>
+      </c>
+      <c r="C300" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D300" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="E300" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F300" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G300" s="13">
+        <v>77</v>
+      </c>
+      <c r="H300" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I300" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="301" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A301" s="7">
+        <v>282</v>
+      </c>
+      <c r="B301" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="C301" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D301" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="E301" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F301" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G301" s="13">
+        <v>65</v>
+      </c>
+      <c r="H301" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I301" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="302" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A302" s="7">
+        <v>283</v>
+      </c>
+      <c r="B302" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="C302" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D302" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="E302" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F302" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G302" s="13">
+        <v>17</v>
+      </c>
+      <c r="H302" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I302" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="303" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A303" s="7">
+        <v>284</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="C303" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D303" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="E303" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F303" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G303" s="13">
+        <v>75</v>
+      </c>
+      <c r="H303" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I303" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="304" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A304" s="7">
+        <v>285</v>
+      </c>
+      <c r="B304" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="C304" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D304" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="E304" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F304" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G304" s="13">
+        <v>13</v>
+      </c>
+      <c r="H304" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I304" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="305" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A305" s="7">
+        <v>286</v>
+      </c>
+      <c r="B305" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="C305" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D305" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="E305" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F305" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G305" s="13">
+        <v>71</v>
+      </c>
+      <c r="H305" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I305" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="306" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A306" s="7">
+        <v>287</v>
+      </c>
+      <c r="B306" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="C306" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D306" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="E306" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F306" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G306" s="13">
+        <v>17</v>
+      </c>
+      <c r="H306" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I306" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="307" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A307" s="7">
+        <v>288</v>
+      </c>
+      <c r="B307" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="C307" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D307" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="E307" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F307" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G307" s="13">
+        <v>22</v>
+      </c>
+      <c r="H307" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I307" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="308" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A308" s="7">
+        <v>289</v>
+      </c>
+      <c r="B308" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="C308" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D308" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="E308" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F308" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G308" s="13">
+        <v>52</v>
+      </c>
+      <c r="H308" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I308" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="309" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A309" s="7">
+        <v>290</v>
+      </c>
+      <c r="B309" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="C309" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D309" s="5" t="s">
+        <v>650</v>
+      </c>
+      <c r="E309" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F309" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G309" s="13">
+        <v>67</v>
+      </c>
+      <c r="H309" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I309" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="310" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A310" s="7">
+        <v>291</v>
+      </c>
+      <c r="B310" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="C310" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D310" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="E310" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F310" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G310" s="13">
+        <v>15</v>
+      </c>
+      <c r="H310" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I310" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="311" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A311" s="7">
+        <v>292</v>
+      </c>
+      <c r="B311" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="C311" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D311" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="E311" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F311" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G311" s="13">
+        <v>53</v>
+      </c>
+      <c r="H311" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I311" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="312" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A312" s="7">
+        <v>293</v>
+      </c>
+      <c r="B312" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="C312" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D312" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="E312" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F312" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G312" s="13">
+        <v>14</v>
+      </c>
+      <c r="H312" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I312" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="313" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A313" s="7">
+        <v>294</v>
+      </c>
+      <c r="B313" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="C313" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D313" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="E313" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F313" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G313" s="13">
+        <v>13</v>
+      </c>
+      <c r="H313" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I313" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="314" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A314" s="7">
+        <v>295</v>
+      </c>
+      <c r="B314" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="C314" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D314" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="E314" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F314" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G314" s="13">
+        <v>45</v>
+      </c>
+      <c r="H314" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I314" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="315" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A315" s="7">
+        <v>296</v>
+      </c>
+      <c r="B315" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="C315" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D315" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="E315" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F315" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G315" s="13">
+        <v>15</v>
+      </c>
+      <c r="H315" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I315" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="316" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A316" s="7">
+        <v>297</v>
+      </c>
+      <c r="B316" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="C316" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D316" s="5" t="s">
+        <v>664</v>
+      </c>
+      <c r="E316" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F316" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G316" s="13">
+        <v>52</v>
+      </c>
+      <c r="H316" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I316" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="317" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A317" s="7">
+        <v>298</v>
+      </c>
+      <c r="B317" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="C317" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D317" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="E317" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F317" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G317" s="13">
+        <v>74</v>
+      </c>
+      <c r="H317" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I317" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="318" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A318" s="7">
+        <v>299</v>
+      </c>
+      <c r="B318" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="C318" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D318" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="E318" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F318" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G318" s="13">
+        <v>68</v>
+      </c>
+      <c r="H318" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I318" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="319" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A319" s="7">
+        <v>300</v>
+      </c>
+      <c r="B319" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="C319" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D319" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="E319" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F319" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G319" s="13">
+        <v>62</v>
+      </c>
+      <c r="H319" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I319" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="320" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A320" s="7">
+        <v>301</v>
+      </c>
+      <c r="B320" s="6" t="s">
+        <v>671</v>
+      </c>
+      <c r="C320" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D320" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="E320" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F320" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G320" s="13">
+        <v>15</v>
+      </c>
+      <c r="H320" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I320" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="321" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A321" s="7">
+        <v>302</v>
+      </c>
+      <c r="B321" s="6" t="s">
+        <v>673</v>
+      </c>
+      <c r="C321" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D321" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="E321" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F321" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G321" s="13">
+        <v>56</v>
+      </c>
+      <c r="H321" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I321" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="322" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A322" s="7">
+        <v>303</v>
+      </c>
+      <c r="B322" s="6" t="s">
+        <v>675</v>
+      </c>
+      <c r="C322" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D322" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="E322" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F322" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G322" s="13">
+        <v>20</v>
+      </c>
+      <c r="H322" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I322" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="323" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A323" s="7">
+        <v>304</v>
+      </c>
+      <c r="B323" s="6" t="s">
+        <v>677</v>
+      </c>
+      <c r="C323" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D323" s="5" t="s">
+        <v>678</v>
+      </c>
+      <c r="E323" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F323" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G323" s="13">
+        <v>58</v>
+      </c>
+      <c r="H323" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I323" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="324" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A324" s="7">
+        <v>305</v>
+      </c>
+      <c r="B324" s="6" t="s">
+        <v>679</v>
+      </c>
+      <c r="C324" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D324" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="E324" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F324" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G324" s="13">
+        <v>62</v>
+      </c>
+      <c r="H324" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I324" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="325" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A325" s="7">
+        <v>306</v>
+      </c>
+      <c r="B325" s="6" t="s">
+        <v>681</v>
+      </c>
+      <c r="C325" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D325" s="5" t="s">
+        <v>682</v>
+      </c>
+      <c r="E325" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F325" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G325" s="13">
+        <v>71</v>
+      </c>
+      <c r="H325" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I325" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="326" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A326" s="7">
+        <v>307</v>
+      </c>
+      <c r="B326" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="C326" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D326" s="5" t="s">
+        <v>684</v>
+      </c>
+      <c r="E326" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F326" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G326" s="13">
+        <v>61</v>
+      </c>
+      <c r="H326" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I326" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="327" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A327" s="7">
+        <v>308</v>
+      </c>
+      <c r="B327" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="C327" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D327" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="E327" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F327" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G327" s="13">
+        <v>14</v>
+      </c>
+      <c r="H327" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I327" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="328" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A328" s="7">
+        <v>309</v>
+      </c>
+      <c r="B328" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="C328" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D328" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="E328" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F328" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G328" s="13">
+        <v>46</v>
+      </c>
+      <c r="H328" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I328" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="329" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A329" s="7">
+        <v>310</v>
+      </c>
+      <c r="B329" s="6" t="s">
+        <v>689</v>
+      </c>
+      <c r="C329" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D329" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="E329" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F329" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G329" s="13">
+        <v>15</v>
+      </c>
+      <c r="H329" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I329" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="330" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A330" s="7">
+        <v>311</v>
+      </c>
+      <c r="B330" s="6" t="s">
+        <v>691</v>
+      </c>
+      <c r="C330" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D330" s="5" t="s">
+        <v>692</v>
+      </c>
+      <c r="E330" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F330" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G330" s="13">
+        <v>59</v>
+      </c>
+      <c r="H330" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I330" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="331" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A331" s="7">
+        <v>312</v>
+      </c>
+      <c r="B331" s="6" t="s">
+        <v>693</v>
+      </c>
+      <c r="C331" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D331" s="5" t="s">
+        <v>694</v>
+      </c>
+      <c r="E331" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F331" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G331" s="13">
+        <v>14</v>
+      </c>
+      <c r="H331" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I331" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="332" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A332" s="7">
+        <v>313</v>
+      </c>
+      <c r="B332" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="C332" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D332" s="5" t="s">
+        <v>696</v>
+      </c>
+      <c r="E332" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F332" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G332" s="13">
+        <v>48</v>
+      </c>
+      <c r="H332" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I332" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="333" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A333" s="7">
+        <v>314</v>
+      </c>
+      <c r="B333" s="6" t="s">
+        <v>697</v>
+      </c>
+      <c r="C333" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D333" s="5" t="s">
+        <v>698</v>
+      </c>
+      <c r="E333" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F333" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G333" s="13">
+        <v>13</v>
+      </c>
+      <c r="H333" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I333" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="334" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A334" s="7">
+        <v>315</v>
+      </c>
+      <c r="B334" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="C334" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D334" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="E334" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F334" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G334" s="13">
+        <v>12</v>
+      </c>
+      <c r="H334" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I334" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="335" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A335" s="7">
+        <v>316</v>
+      </c>
+      <c r="B335" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="C335" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D335" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="E335" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F335" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G335" s="13">
+        <v>37</v>
+      </c>
+      <c r="H335" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I335" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="336" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A336" s="7">
+        <v>317</v>
+      </c>
+      <c r="B336" s="6" t="s">
+        <v>703</v>
+      </c>
+      <c r="C336" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D336" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="E336" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F336" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G336" s="13">
+        <v>14</v>
+      </c>
+      <c r="H336" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I336" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="337" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A337" s="7">
+        <v>318</v>
+      </c>
+      <c r="B337" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="C337" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D337" s="5" t="s">
+        <v>706</v>
+      </c>
+      <c r="E337" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F337" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G337" s="13">
+        <v>59</v>
+      </c>
+      <c r="H337" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I337" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="338" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A338" s="7">
+        <v>319</v>
+      </c>
+      <c r="B338" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="C338" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D338" s="5" t="s">
+        <v>708</v>
+      </c>
+      <c r="E338" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F338" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G338" s="13">
+        <v>14</v>
+      </c>
+      <c r="H338" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I338" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="339" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A339" s="7">
+        <v>320</v>
+      </c>
+      <c r="B339" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="C339" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="D339" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="E339" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F339" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G339" s="13">
+        <v>15</v>
+      </c>
+      <c r="H339" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I339" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="340" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A340" s="11" t="s">
+        <v>711</v>
+      </c>
+      <c r="B340" s="11"/>
+      <c r="C340" s="11"/>
+      <c r="D340" s="11"/>
+      <c r="E340" s="11"/>
+      <c r="F340" s="11"/>
+      <c r="G340" s="11"/>
+      <c r="H340" s="11"/>
+      <c r="I340" s="11"/>
+    </row>
+    <row r="341" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A341" s="7">
+        <v>321</v>
+      </c>
+      <c r="B341" s="6" t="s">
+        <v>712</v>
+      </c>
+      <c r="C341" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D341" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="E341" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F341" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G341" s="13">
+        <v>24</v>
+      </c>
+      <c r="H341" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I341" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="342" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A342" s="7">
+        <v>322</v>
+      </c>
+      <c r="B342" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="C342" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D342" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="E342" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F342" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G342" s="13">
+        <v>32</v>
+      </c>
+      <c r="H342" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I342" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="343" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A343" s="7">
+        <v>323</v>
+      </c>
+      <c r="B343" s="6" t="s">
+        <v>717</v>
+      </c>
+      <c r="C343" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D343" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="E343" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F343" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G343" s="13">
+        <v>13</v>
+      </c>
+      <c r="H343" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I343" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="344" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A344" s="7">
+        <v>324</v>
+      </c>
+      <c r="B344" s="6" t="s">
+        <v>719</v>
+      </c>
+      <c r="C344" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D344" s="5" t="s">
+        <v>720</v>
+      </c>
+      <c r="E344" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F344" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G344" s="13">
+        <v>58</v>
+      </c>
+      <c r="H344" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I344" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="345" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A345" s="7">
+        <v>325</v>
+      </c>
+      <c r="B345" s="6" t="s">
+        <v>721</v>
+      </c>
+      <c r="C345" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D345" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="E345" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F345" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G345" s="13">
+        <v>20</v>
+      </c>
+      <c r="H345" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I345" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="346" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A346" s="7">
+        <v>326</v>
+      </c>
+      <c r="B346" s="6" t="s">
+        <v>723</v>
+      </c>
+      <c r="C346" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D346" s="5" t="s">
+        <v>724</v>
+      </c>
+      <c r="E346" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F346" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G346" s="13">
+        <v>10</v>
+      </c>
+      <c r="H346" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I346" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="347" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A347" s="7">
+        <v>327</v>
+      </c>
+      <c r="B347" s="6" t="s">
+        <v>725</v>
+      </c>
+      <c r="C347" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D347" s="5" t="s">
+        <v>726</v>
+      </c>
+      <c r="E347" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F347" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G347" s="13">
+        <v>14</v>
+      </c>
+      <c r="H347" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I347" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="348" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A348" s="7">
+        <v>328</v>
+      </c>
+      <c r="B348" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="C348" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D348" s="5" t="s">
+        <v>728</v>
+      </c>
+      <c r="E348" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F348" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G348" s="13">
+        <v>12</v>
+      </c>
+      <c r="H348" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I348" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="349" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A349" s="7">
+        <v>329</v>
+      </c>
+      <c r="B349" s="6" t="s">
+        <v>729</v>
+      </c>
+      <c r="C349" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D349" s="5" t="s">
+        <v>730</v>
+      </c>
+      <c r="E349" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F349" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G349" s="13">
+        <v>14</v>
+      </c>
+      <c r="H349" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I349" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="350" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A350" s="7">
+        <v>330</v>
+      </c>
+      <c r="B350" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="C350" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D350" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="E350" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F350" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G350" s="13">
+        <v>12</v>
+      </c>
+      <c r="H350" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I350" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="351" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A351" s="7">
+        <v>331</v>
+      </c>
+      <c r="B351" s="6" t="s">
+        <v>733</v>
+      </c>
+      <c r="C351" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D351" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="E351" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F351" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G351" s="13">
+        <v>14</v>
+      </c>
+      <c r="H351" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I351" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="352" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A352" s="7">
+        <v>332</v>
+      </c>
+      <c r="B352" s="6" t="s">
+        <v>735</v>
+      </c>
+      <c r="C352" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D352" s="5" t="s">
+        <v>736</v>
+      </c>
+      <c r="E352" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F352" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G352" s="13">
+        <v>11</v>
+      </c>
+      <c r="H352" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I352" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="353" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A353" s="7">
+        <v>333</v>
+      </c>
+      <c r="B353" s="6" t="s">
+        <v>737</v>
+      </c>
+      <c r="C353" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D353" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="E353" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F353" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G353" s="13">
+        <v>14</v>
+      </c>
+      <c r="H353" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I353" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="354" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A354" s="7">
+        <v>334</v>
+      </c>
+      <c r="B354" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="C354" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D354" s="5" t="s">
+        <v>740</v>
+      </c>
+      <c r="E354" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F354" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G354" s="13">
+        <v>13</v>
+      </c>
+      <c r="H354" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I354" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="355" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A355" s="7">
+        <v>335</v>
+      </c>
+      <c r="B355" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="C355" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D355" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="E355" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F355" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G355" s="13">
+        <v>14</v>
+      </c>
+      <c r="H355" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I355" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="356" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A356" s="7">
+        <v>336</v>
+      </c>
+      <c r="B356" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="C356" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D356" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="E356" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F356" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G356" s="13">
+        <v>12</v>
+      </c>
+      <c r="H356" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I356" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="357" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A357" s="7">
+        <v>337</v>
+      </c>
+      <c r="B357" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="C357" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D357" s="5" t="s">
+        <v>746</v>
+      </c>
+      <c r="E357" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F357" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G357" s="13">
+        <v>12</v>
+      </c>
+      <c r="H357" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I357" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="358" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A358" s="7">
+        <v>338</v>
+      </c>
+      <c r="B358" s="6" t="s">
+        <v>747</v>
+      </c>
+      <c r="C358" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D358" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="E358" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F358" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G358" s="13">
+        <v>11</v>
+      </c>
+      <c r="H358" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I358" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="359" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A359" s="7">
+        <v>339</v>
+      </c>
+      <c r="B359" s="6" t="s">
+        <v>749</v>
+      </c>
+      <c r="C359" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D359" s="5" t="s">
+        <v>750</v>
+      </c>
+      <c r="E359" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F359" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G359" s="13">
+        <v>14</v>
+      </c>
+      <c r="H359" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I359" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="360" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A360" s="7">
+        <v>340</v>
+      </c>
+      <c r="B360" s="6" t="s">
+        <v>751</v>
+      </c>
+      <c r="C360" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D360" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="E360" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F360" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G360" s="13">
+        <v>14</v>
+      </c>
+      <c r="H360" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I360" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="361" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A361" s="7">
+        <v>341</v>
+      </c>
+      <c r="B361" s="6" t="s">
+        <v>753</v>
+      </c>
+      <c r="C361" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D361" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="E361" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F361" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G361" s="13">
+        <v>11</v>
+      </c>
+      <c r="H361" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I361" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="362" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A362" s="7">
+        <v>342</v>
+      </c>
+      <c r="B362" s="6" t="s">
+        <v>755</v>
+      </c>
+      <c r="C362" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D362" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="E362" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F362" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G362" s="13">
+        <v>12</v>
+      </c>
+      <c r="H362" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I362" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="363" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A363" s="7">
+        <v>343</v>
+      </c>
+      <c r="B363" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="C363" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D363" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="E363" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F363" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G363" s="13">
+        <v>12</v>
+      </c>
+      <c r="H363" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I363" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="364" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A364" s="7">
+        <v>344</v>
+      </c>
+      <c r="B364" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="C364" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D364" s="5" t="s">
+        <v>760</v>
+      </c>
+      <c r="E364" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F364" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G364" s="13">
+        <v>11</v>
+      </c>
+      <c r="H364" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I364" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="365" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A365" s="7">
+        <v>345</v>
+      </c>
+      <c r="B365" s="6" t="s">
+        <v>761</v>
+      </c>
+      <c r="C365" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D365" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="E365" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F365" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G365" s="13">
+        <v>13</v>
+      </c>
+      <c r="H365" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I365" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="366" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A366" s="7">
+        <v>346</v>
+      </c>
+      <c r="B366" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="C366" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D366" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="E366" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F366" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G366" s="13">
+        <v>14</v>
+      </c>
+      <c r="H366" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I366" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="367" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A367" s="7">
+        <v>347</v>
+      </c>
+      <c r="B367" s="6" t="s">
+        <v>765</v>
+      </c>
+      <c r="C367" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D367" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="E367" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F367" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G367" s="13">
+        <v>13</v>
+      </c>
+      <c r="H367" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I367" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="368" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A368" s="7">
+        <v>348</v>
+      </c>
+      <c r="B368" s="6" t="s">
+        <v>767</v>
+      </c>
+      <c r="C368" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D368" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="E368" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F368" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G368" s="13">
+        <v>12</v>
+      </c>
+      <c r="H368" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I368" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="369" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A369" s="7">
+        <v>349</v>
+      </c>
+      <c r="B369" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="C369" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D369" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="E369" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F369" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G369" s="13">
+        <v>11</v>
+      </c>
+      <c r="H369" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I369" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="370" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A370" s="7">
+        <v>350</v>
+      </c>
+      <c r="B370" s="6" t="s">
+        <v>771</v>
+      </c>
+      <c r="C370" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D370" s="5" t="s">
+        <v>772</v>
+      </c>
+      <c r="E370" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F370" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G370" s="13">
+        <v>13</v>
+      </c>
+      <c r="H370" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I370" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="371" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A371" s="7">
+        <v>351</v>
+      </c>
+      <c r="B371" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="C371" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D371" s="5" t="s">
+        <v>774</v>
+      </c>
+      <c r="E371" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F371" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G371" s="13">
+        <v>13</v>
+      </c>
+      <c r="H371" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I371" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="372" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A372" s="7">
+        <v>352</v>
+      </c>
+      <c r="B372" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="C372" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D372" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="E372" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F372" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G372" s="13">
+        <v>12</v>
+      </c>
+      <c r="H372" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I372" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="373" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A373" s="7">
+        <v>353</v>
+      </c>
+      <c r="B373" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="C373" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D373" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="E373" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F373" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G373" s="13">
+        <v>13</v>
+      </c>
+      <c r="H373" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I373" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="374" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A374" s="7">
+        <v>354</v>
+      </c>
+      <c r="B374" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="C374" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D374" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="E374" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F374" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G374" s="13">
+        <v>12</v>
+      </c>
+      <c r="H374" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I374" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="375" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A375" s="7">
+        <v>355</v>
+      </c>
+      <c r="B375" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="C375" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D375" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="E375" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F375" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G375" s="13">
+        <v>12</v>
+      </c>
+      <c r="H375" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I375" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="376" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A376" s="7">
+        <v>356</v>
+      </c>
+      <c r="B376" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="C376" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D376" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E376" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F376" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G376" s="13">
+        <v>12</v>
+      </c>
+      <c r="H376" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I376" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="377" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A377" s="7">
+        <v>357</v>
+      </c>
+      <c r="B377" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="C377" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D377" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="E377" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F377" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G377" s="13">
+        <v>12</v>
+      </c>
+      <c r="H377" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I377" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="378" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A378" s="7">
+        <v>358</v>
+      </c>
+      <c r="B378" s="6" t="s">
+        <v>787</v>
+      </c>
+      <c r="C378" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D378" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="E378" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F378" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G378" s="13">
+        <v>12</v>
+      </c>
+      <c r="H378" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I378" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="379" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A379" s="7">
+        <v>359</v>
+      </c>
+      <c r="B379" s="6" t="s">
+        <v>789</v>
+      </c>
+      <c r="C379" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D379" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="E379" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F379" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G379" s="13">
+        <v>12</v>
+      </c>
+      <c r="H379" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I379" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="380" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A380" s="7">
+        <v>360</v>
+      </c>
+      <c r="B380" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="C380" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D380" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="E380" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F380" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G380" s="13">
+        <v>11</v>
+      </c>
+      <c r="H380" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I380" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="19">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A44:I44"/>
@@ -9843,6 +13750,9 @@
     <mergeCell ref="A235:I235"/>
     <mergeCell ref="A246:I246"/>
     <mergeCell ref="A257:I257"/>
+    <mergeCell ref="A268:I268"/>
+    <mergeCell ref="A299:I299"/>
+    <mergeCell ref="A340:I340"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
